--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -1816,11 +1816,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="26" min="2" width="30"/>
+    <col customWidth="true" max="1" min="1" width="9"/>
+    <col customWidth="true" max="3" min="2" width="20"/>
+    <col customWidth="true" max="26" min="4" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3123,7 +3127,8 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup orientation="landscape"/>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -3131,7 +3136,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3516,7 +3521,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -11309,7 +11314,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -11699,7 +11704,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -12,17 +12,19 @@
     <sheet name="Pool Draw" sheetId="3" r:id="rId5"/>
     <sheet name="Pool Matches" sheetId="4" r:id="rId6"/>
     <sheet name="Elimination Matches" sheetId="5" r:id="rId7"/>
-    <sheet name="Names to Print" sheetId="6" r:id="rId8"/>
     <sheet name="Tree 1" sheetId="8" r:id="rId11"/>
     <sheet name="Tree 2" sheetId="9" r:id="rId12"/>
     <sheet name="Tree 3" sheetId="10" r:id="rId13"/>
     <sheet name="Tree 4" sheetId="11" r:id="rId14"/>
-    <sheet name="Tags" sheetId="12" r:id="rId15"/>
+    <sheet name="Names to Print A" sheetId="12" r:id="rId15"/>
+    <sheet name="Names to Print B" sheetId="13" r:id="rId16"/>
+    <sheet name="Tags" sheetId="14" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$66</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$153</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$91</definedName>
+    <definedName localSheetId="9" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$46</definedName>
+    <definedName localSheetId="10" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$45</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$271</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="404">
   <si>
     <t>Number of pools</t>
   </si>
@@ -1214,10 +1216,13 @@
     <t>Round 4 - Match 56</t>
   </si>
   <si>
-    <t>Round 5 - Match 0</t>
-  </si>
-  <si>
-    <t>Round 6 - Match 0</t>
+    <t>Round 5 - Match 57</t>
+  </si>
+  <si>
+    <t>Round 5 - Match 58</t>
+  </si>
+  <si>
+    <t>Round 6 - Match 59</t>
   </si>
   <si>
     <t>Tournament Summary</t>
@@ -3883,6 +3888,798 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D3</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D4</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D5</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D6</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D7</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D8</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D9</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D10</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D11</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D12</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D13</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D14</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B13" s="27" t="str">
+        <f>data!D15</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" s="27" t="str">
+        <f>data!D16</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f>data!D17</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="B16" s="27" t="str">
+        <f>data!D18</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="B17" s="27" t="str">
+        <f>data!D19</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" s="27" t="str">
+        <f>data!D20</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B19" s="27" t="str">
+        <f>data!D21</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" s="27" t="str">
+        <f>data!D22</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="B21" s="27" t="str">
+        <f>data!D23</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="B22" s="27" t="str">
+        <f>data!D24</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" s="27" t="str">
+        <f>data!D25</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="B24" s="27" t="str">
+        <f>data!D26</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B25" s="27" t="str">
+        <f>data!D27</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B26" s="27" t="str">
+        <f>data!D28</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="B27" s="27" t="str">
+        <f>data!D29</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="B28" s="27" t="str">
+        <f>data!D30</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="B29" s="27" t="str">
+        <f>data!D31</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B30" s="27" t="str">
+        <f>data!D32</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="B31" s="27" t="str">
+        <f>data!D33</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="B32" s="27" t="str">
+        <f>data!D34</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B33" s="27" t="str">
+        <f>data!D35</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B34" s="27" t="str">
+        <f>data!D36</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="B35" s="27" t="str">
+        <f>data!D37</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B36" s="27" t="str">
+        <f>data!D38</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="B37" s="27" t="str">
+        <f>data!D39</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B38" s="27" t="str">
+        <f>data!D40</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="B39" s="27" t="str">
+        <f>data!D41</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="B40" s="27" t="str">
+        <f>data!D42</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="B41" s="27" t="str">
+        <f>data!D43</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="B42" s="27" t="str">
+        <f>data!D44</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="B43" s="27" t="str">
+        <f>data!D45</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B44" s="27" t="str">
+        <f>data!D46</f>
+      </c>
+    </row>
+    <row r="45" ht="270" customHeight="true">
+      <c r="A45" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="B45" s="27" t="str">
+        <f>data!D47</f>
+      </c>
+    </row>
+    <row r="46" ht="270" customHeight="true">
+      <c r="A46" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="B46" s="27" t="str">
+        <f>data!D48</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="15" manualBreakCount="15">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+    <brk id="45" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D49</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D50</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D51</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D52</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D53</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D54</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D55</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D56</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D57</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D58</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D59</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D60</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="B13" s="27" t="str">
+        <f>data!D61</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="B14" s="27" t="str">
+        <f>data!D62</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f>data!D63</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="B16" s="27" t="str">
+        <f>data!D64</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="B17" s="27" t="str">
+        <f>data!D65</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="B18" s="27" t="str">
+        <f>data!D66</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="B19" s="27" t="str">
+        <f>data!D67</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="B20" s="27" t="str">
+        <f>data!D68</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="B21" s="27" t="str">
+        <f>data!D69</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="B22" s="27" t="str">
+        <f>data!D70</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="B23" s="27" t="str">
+        <f>data!D71</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="B24" s="27" t="str">
+        <f>data!D72</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="B25" s="27" t="str">
+        <f>data!D73</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="B26" s="27" t="str">
+        <f>data!D74</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="B27" s="27" t="str">
+        <f>data!D75</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="B28" s="27" t="str">
+        <f>data!D76</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="B29" s="27" t="str">
+        <f>data!D77</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="B30" s="27" t="str">
+        <f>data!D78</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="B31" s="27" t="str">
+        <f>data!D79</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="B32" s="27" t="str">
+        <f>data!D80</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="B33" s="27" t="str">
+        <f>data!D81</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" s="27" t="str">
+        <f>data!D82</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="B35" s="27" t="str">
+        <f>data!D83</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="B36" s="27" t="str">
+        <f>data!D84</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="B37" s="27" t="str">
+        <f>data!D85</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="B38" s="27" t="str">
+        <f>data!D86</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="B39" s="27" t="str">
+        <f>data!D87</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B40" s="27" t="str">
+        <f>data!D88</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="B41" s="27" t="str">
+        <f>data!D89</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="B42" s="27" t="str">
+        <f>data!D90</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="B43" s="27" t="str">
+        <f>data!D91</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="B44" s="27" t="str">
+        <f>data!D92</f>
+      </c>
+    </row>
+    <row r="45" ht="270" customHeight="true">
+      <c r="A45" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="B45" s="27" t="str">
+        <f>data!D93</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="15" manualBreakCount="15">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+    <brk id="45" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
@@ -5096,7 +5893,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -5107,7 +5904,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
@@ -5117,7 +5914,7 @@
     </row>
     <row r="15">
       <c r="E15" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
@@ -5127,7 +5924,7 @@
     </row>
     <row r="16">
       <c r="E16" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
@@ -5137,7 +5934,7 @@
     </row>
     <row r="17">
       <c r="E17" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
@@ -5147,7 +5944,7 @@
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -5157,7 +5954,7 @@
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -10335,7 +11132,7 @@
       <c r="F246" s="13"/>
       <c r="G246" s="13"/>
       <c r="I246" s="13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J246" s="13"/>
       <c r="K246" s="13"/>
@@ -10410,7 +11207,7 @@
     </row>
     <row r="259">
       <c r="A259" s="13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B259" s="13"/>
       <c r="C259" s="13"/>
@@ -10432,7 +11229,7 @@
     </row>
     <row r="261">
       <c r="A261" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O250)</f>
+        <f>CONCATENATE("M 58 ",O250)</f>
       </c>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
@@ -10440,7 +11237,7 @@
       <c r="E261" s="14"/>
       <c r="F261" s="14"/>
       <c r="G261" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O250)</f>
+        <f>CONCATENATE("M 57 ",G250)</f>
       </c>
     </row>
     <row r="263">
@@ -10535,781 +11332,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" style="9" width="30"/>
-    <col customWidth="true" max="2" min="2" style="10" width="160"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="B1" s="27" t="str">
-        <f>data!D3</f>
-      </c>
-    </row>
-    <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="B2" s="27" t="str">
-        <f>data!D4</f>
-      </c>
-    </row>
-    <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="B3" s="27" t="str">
-        <f>data!D5</f>
-      </c>
-    </row>
-    <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="B4" s="27" t="str">
-        <f>data!D6</f>
-      </c>
-    </row>
-    <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="B5" s="27" t="str">
-        <f>data!D7</f>
-      </c>
-    </row>
-    <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="B6" s="27" t="str">
-        <f>data!D8</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="B7" s="27" t="str">
-        <f>data!D9</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="B8" s="27" t="str">
-        <f>data!D10</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="B9" s="27" t="str">
-        <f>data!D11</f>
-      </c>
-    </row>
-    <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="B10" s="27" t="str">
-        <f>data!D12</f>
-      </c>
-    </row>
-    <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="B11" s="27" t="str">
-        <f>data!D13</f>
-      </c>
-    </row>
-    <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="B12" s="27" t="str">
-        <f>data!D14</f>
-      </c>
-    </row>
-    <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="B13" s="27" t="str">
-        <f>data!D15</f>
-      </c>
-    </row>
-    <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="B14" s="27" t="str">
-        <f>data!D16</f>
-      </c>
-    </row>
-    <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="B15" s="27" t="str">
-        <f>data!D17</f>
-      </c>
-    </row>
-    <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="B16" s="27" t="str">
-        <f>data!D18</f>
-      </c>
-    </row>
-    <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="B17" s="27" t="str">
-        <f>data!D19</f>
-      </c>
-    </row>
-    <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B18" s="27" t="str">
-        <f>data!D20</f>
-      </c>
-    </row>
-    <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="B19" s="27" t="str">
-        <f>data!D21</f>
-      </c>
-    </row>
-    <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="B20" s="27" t="str">
-        <f>data!D22</f>
-      </c>
-    </row>
-    <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="B21" s="27" t="str">
-        <f>data!D23</f>
-      </c>
-    </row>
-    <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="B22" s="27" t="str">
-        <f>data!D24</f>
-      </c>
-    </row>
-    <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="B23" s="27" t="str">
-        <f>data!D25</f>
-      </c>
-    </row>
-    <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="B24" s="27" t="str">
-        <f>data!D26</f>
-      </c>
-    </row>
-    <row r="25" ht="270" customHeight="true">
-      <c r="A25" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="B25" s="27" t="str">
-        <f>data!D27</f>
-      </c>
-    </row>
-    <row r="26" ht="270" customHeight="true">
-      <c r="A26" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="B26" s="27" t="str">
-        <f>data!D28</f>
-      </c>
-    </row>
-    <row r="27" ht="270" customHeight="true">
-      <c r="A27" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="B27" s="27" t="str">
-        <f>data!D29</f>
-      </c>
-    </row>
-    <row r="28" ht="270" customHeight="true">
-      <c r="A28" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="B28" s="27" t="str">
-        <f>data!D30</f>
-      </c>
-    </row>
-    <row r="29" ht="270" customHeight="true">
-      <c r="A29" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="B29" s="27" t="str">
-        <f>data!D31</f>
-      </c>
-    </row>
-    <row r="30" ht="270" customHeight="true">
-      <c r="A30" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="B30" s="27" t="str">
-        <f>data!D32</f>
-      </c>
-    </row>
-    <row r="31" ht="270" customHeight="true">
-      <c r="A31" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="B31" s="27" t="str">
-        <f>data!D33</f>
-      </c>
-    </row>
-    <row r="32" ht="270" customHeight="true">
-      <c r="A32" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="B32" s="27" t="str">
-        <f>data!D34</f>
-      </c>
-    </row>
-    <row r="33" ht="270" customHeight="true">
-      <c r="A33" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B33" s="27" t="str">
-        <f>data!D35</f>
-      </c>
-    </row>
-    <row r="34" ht="270" customHeight="true">
-      <c r="A34" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="B34" s="27" t="str">
-        <f>data!D36</f>
-      </c>
-    </row>
-    <row r="35" ht="270" customHeight="true">
-      <c r="A35" s="26" t="s">
-        <v>279</v>
-      </c>
-      <c r="B35" s="27" t="str">
-        <f>data!D37</f>
-      </c>
-    </row>
-    <row r="36" ht="270" customHeight="true">
-      <c r="A36" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="B36" s="27" t="str">
-        <f>data!D38</f>
-      </c>
-    </row>
-    <row r="37" ht="270" customHeight="true">
-      <c r="A37" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="B37" s="27" t="str">
-        <f>data!D39</f>
-      </c>
-    </row>
-    <row r="38" ht="270" customHeight="true">
-      <c r="A38" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="B38" s="27" t="str">
-        <f>data!D40</f>
-      </c>
-    </row>
-    <row r="39" ht="270" customHeight="true">
-      <c r="A39" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="B39" s="27" t="str">
-        <f>data!D41</f>
-      </c>
-    </row>
-    <row r="40" ht="270" customHeight="true">
-      <c r="A40" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="B40" s="27" t="str">
-        <f>data!D42</f>
-      </c>
-    </row>
-    <row r="41" ht="270" customHeight="true">
-      <c r="A41" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="B41" s="27" t="str">
-        <f>data!D43</f>
-      </c>
-    </row>
-    <row r="42" ht="270" customHeight="true">
-      <c r="A42" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="B42" s="27" t="str">
-        <f>data!D44</f>
-      </c>
-    </row>
-    <row r="43" ht="270" customHeight="true">
-      <c r="A43" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="B43" s="27" t="str">
-        <f>data!D45</f>
-      </c>
-    </row>
-    <row r="44" ht="270" customHeight="true">
-      <c r="A44" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="B44" s="27" t="str">
-        <f>data!D46</f>
-      </c>
-    </row>
-    <row r="45" ht="270" customHeight="true">
-      <c r="A45" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="B45" s="27" t="str">
-        <f>data!D47</f>
-      </c>
-    </row>
-    <row r="46" ht="270" customHeight="true">
-      <c r="A46" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="B46" s="27" t="str">
-        <f>data!D48</f>
-      </c>
-    </row>
-    <row r="47" ht="270" customHeight="true">
-      <c r="A47" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="B47" s="27" t="str">
-        <f>data!D49</f>
-      </c>
-    </row>
-    <row r="48" ht="270" customHeight="true">
-      <c r="A48" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="B48" s="27" t="str">
-        <f>data!D50</f>
-      </c>
-    </row>
-    <row r="49" ht="270" customHeight="true">
-      <c r="A49" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="B49" s="27" t="str">
-        <f>data!D51</f>
-      </c>
-    </row>
-    <row r="50" ht="270" customHeight="true">
-      <c r="A50" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="B50" s="27" t="str">
-        <f>data!D52</f>
-      </c>
-    </row>
-    <row r="51" ht="270" customHeight="true">
-      <c r="A51" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="B51" s="27" t="str">
-        <f>data!D53</f>
-      </c>
-    </row>
-    <row r="52" ht="270" customHeight="true">
-      <c r="A52" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="B52" s="27" t="str">
-        <f>data!D54</f>
-      </c>
-    </row>
-    <row r="53" ht="270" customHeight="true">
-      <c r="A53" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="B53" s="27" t="str">
-        <f>data!D55</f>
-      </c>
-    </row>
-    <row r="54" ht="270" customHeight="true">
-      <c r="A54" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="B54" s="27" t="str">
-        <f>data!D56</f>
-      </c>
-    </row>
-    <row r="55" ht="270" customHeight="true">
-      <c r="A55" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="B55" s="27" t="str">
-        <f>data!D57</f>
-      </c>
-    </row>
-    <row r="56" ht="270" customHeight="true">
-      <c r="A56" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="B56" s="27" t="str">
-        <f>data!D58</f>
-      </c>
-    </row>
-    <row r="57" ht="270" customHeight="true">
-      <c r="A57" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="B57" s="27" t="str">
-        <f>data!D59</f>
-      </c>
-    </row>
-    <row r="58" ht="270" customHeight="true">
-      <c r="A58" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="B58" s="27" t="str">
-        <f>data!D60</f>
-      </c>
-    </row>
-    <row r="59" ht="270" customHeight="true">
-      <c r="A59" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="B59" s="27" t="str">
-        <f>data!D61</f>
-      </c>
-    </row>
-    <row r="60" ht="270" customHeight="true">
-      <c r="A60" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="B60" s="27" t="str">
-        <f>data!D62</f>
-      </c>
-    </row>
-    <row r="61" ht="270" customHeight="true">
-      <c r="A61" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="B61" s="27" t="str">
-        <f>data!D63</f>
-      </c>
-    </row>
-    <row r="62" ht="270" customHeight="true">
-      <c r="A62" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="B62" s="27" t="str">
-        <f>data!D64</f>
-      </c>
-    </row>
-    <row r="63" ht="270" customHeight="true">
-      <c r="A63" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="B63" s="27" t="str">
-        <f>data!D65</f>
-      </c>
-    </row>
-    <row r="64" ht="270" customHeight="true">
-      <c r="A64" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="B64" s="27" t="str">
-        <f>data!D66</f>
-      </c>
-    </row>
-    <row r="65" ht="270" customHeight="true">
-      <c r="A65" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="B65" s="27" t="str">
-        <f>data!D67</f>
-      </c>
-    </row>
-    <row r="66" ht="270" customHeight="true">
-      <c r="A66" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="B66" s="27" t="str">
-        <f>data!D68</f>
-      </c>
-    </row>
-    <row r="67" ht="270" customHeight="true">
-      <c r="A67" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="B67" s="27" t="str">
-        <f>data!D69</f>
-      </c>
-    </row>
-    <row r="68" ht="270" customHeight="true">
-      <c r="A68" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="B68" s="27" t="str">
-        <f>data!D70</f>
-      </c>
-    </row>
-    <row r="69" ht="270" customHeight="true">
-      <c r="A69" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="B69" s="27" t="str">
-        <f>data!D71</f>
-      </c>
-    </row>
-    <row r="70" ht="270" customHeight="true">
-      <c r="A70" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="B70" s="27" t="str">
-        <f>data!D72</f>
-      </c>
-    </row>
-    <row r="71" ht="270" customHeight="true">
-      <c r="A71" s="26" t="s">
-        <v>315</v>
-      </c>
-      <c r="B71" s="27" t="str">
-        <f>data!D73</f>
-      </c>
-    </row>
-    <row r="72" ht="270" customHeight="true">
-      <c r="A72" s="26" t="s">
-        <v>316</v>
-      </c>
-      <c r="B72" s="27" t="str">
-        <f>data!D74</f>
-      </c>
-    </row>
-    <row r="73" ht="270" customHeight="true">
-      <c r="A73" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="B73" s="27" t="str">
-        <f>data!D75</f>
-      </c>
-    </row>
-    <row r="74" ht="270" customHeight="true">
-      <c r="A74" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="B74" s="27" t="str">
-        <f>data!D76</f>
-      </c>
-    </row>
-    <row r="75" ht="270" customHeight="true">
-      <c r="A75" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="B75" s="27" t="str">
-        <f>data!D77</f>
-      </c>
-    </row>
-    <row r="76" ht="270" customHeight="true">
-      <c r="A76" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="B76" s="27" t="str">
-        <f>data!D78</f>
-      </c>
-    </row>
-    <row r="77" ht="270" customHeight="true">
-      <c r="A77" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="B77" s="27" t="str">
-        <f>data!D79</f>
-      </c>
-    </row>
-    <row r="78" ht="270" customHeight="true">
-      <c r="A78" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="B78" s="27" t="str">
-        <f>data!D80</f>
-      </c>
-    </row>
-    <row r="79" ht="270" customHeight="true">
-      <c r="A79" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="B79" s="27" t="str">
-        <f>data!D81</f>
-      </c>
-    </row>
-    <row r="80" ht="270" customHeight="true">
-      <c r="A80" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="B80" s="27" t="str">
-        <f>data!D82</f>
-      </c>
-    </row>
-    <row r="81" ht="270" customHeight="true">
-      <c r="A81" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="B81" s="27" t="str">
-        <f>data!D83</f>
-      </c>
-    </row>
-    <row r="82" ht="270" customHeight="true">
-      <c r="A82" s="26" t="s">
-        <v>326</v>
-      </c>
-      <c r="B82" s="27" t="str">
-        <f>data!D84</f>
-      </c>
-    </row>
-    <row r="83" ht="270" customHeight="true">
-      <c r="A83" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="B83" s="27" t="str">
-        <f>data!D85</f>
-      </c>
-    </row>
-    <row r="84" ht="270" customHeight="true">
-      <c r="A84" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="B84" s="27" t="str">
-        <f>data!D86</f>
-      </c>
-    </row>
-    <row r="85" ht="270" customHeight="true">
-      <c r="A85" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="B85" s="27" t="str">
-        <f>data!D87</f>
-      </c>
-    </row>
-    <row r="86" ht="270" customHeight="true">
-      <c r="A86" s="26" t="s">
-        <v>330</v>
-      </c>
-      <c r="B86" s="27" t="str">
-        <f>data!D88</f>
-      </c>
-    </row>
-    <row r="87" ht="270" customHeight="true">
-      <c r="A87" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="B87" s="27" t="str">
-        <f>data!D89</f>
-      </c>
-    </row>
-    <row r="88" ht="270" customHeight="true">
-      <c r="A88" s="26" t="s">
-        <v>332</v>
-      </c>
-      <c r="B88" s="27" t="str">
-        <f>data!D90</f>
-      </c>
-    </row>
-    <row r="89" ht="270" customHeight="true">
-      <c r="A89" s="26" t="s">
-        <v>333</v>
-      </c>
-      <c r="B89" s="27" t="str">
-        <f>data!D91</f>
-      </c>
-    </row>
-    <row r="90" ht="270" customHeight="true">
-      <c r="A90" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="B90" s="27" t="str">
-        <f>data!D92</f>
-      </c>
-    </row>
-    <row r="91" ht="270" customHeight="true">
-      <c r="A91" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="B91" s="27" t="str">
-        <f>data!D93</f>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="30" manualBreakCount="30">
-    <brk id="3" max="16383" man="true"/>
-    <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
-    <brk id="12" max="16383" man="true"/>
-    <brk id="15" max="16383" man="true"/>
-    <brk id="18" max="16383" man="true"/>
-    <brk id="21" max="16383" man="true"/>
-    <brk id="24" max="16383" man="true"/>
-    <brk id="27" max="16383" man="true"/>
-    <brk id="30" max="16383" man="true"/>
-    <brk id="33" max="16383" man="true"/>
-    <brk id="36" max="16383" man="true"/>
-    <brk id="39" max="16383" man="true"/>
-    <brk id="42" max="16383" man="true"/>
-    <brk id="45" max="16383" man="true"/>
-    <brk id="48" max="16383" man="true"/>
-    <brk id="51" max="16383" man="true"/>
-    <brk id="54" max="16383" man="true"/>
-    <brk id="57" max="16383" man="true"/>
-    <brk id="60" max="16383" man="true"/>
-    <brk id="63" max="16383" man="true"/>
-    <brk id="66" max="16383" man="true"/>
-    <brk id="69" max="16383" man="true"/>
-    <brk id="72" max="16383" man="true"/>
-    <brk id="75" max="16383" man="true"/>
-    <brk id="78" max="16383" man="true"/>
-    <brk id="81" max="16383" man="true"/>
-    <brk id="84" max="16383" man="true"/>
-    <brk id="87" max="16383" man="true"/>
-    <brk id="90" max="16383" man="true"/>
-  </rowBreaks>
-  <colBreaks/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -3215,7 +3215,7 @@
         <f>"2. " &amp; data!$B$50</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G38)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
       </c>
     </row>
     <row r="7">
@@ -3236,7 +3236,7 @@
         <f>'data'!$A$54</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G22)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G18)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3259,7 +3259,7 @@
         <f>"2. " &amp; data!$B$53</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G56)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3276,7 +3276,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G72)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3298,7 +3298,7 @@
         <f>"1. " &amp; data!$B$55</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G90)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G87)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3323,7 +3323,7 @@
         <f>"3. " &amp; data!$B$57</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G106)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G103)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3343,7 +3343,7 @@
         <f>'data'!$A$60</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G124)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G121)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3362,7 +3362,7 @@
         <f>"2. " &amp; data!$B$59</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G140)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G137)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3379,7 +3379,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G158)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G155)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3401,7 +3401,7 @@
         <f>"1. " &amp; data!$B$61</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G174)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G171)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3426,7 +3426,7 @@
         <f>"3. " &amp; data!$B$63</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G192)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G189)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3446,7 +3446,7 @@
         <f>'data'!$A$66</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G208)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G205)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -3465,7 +3465,7 @@
         <f>"2. " &amp; data!$B$65</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G226)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G223)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3486,7 +3486,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G242)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G239)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -3506,7 +3506,7 @@
         <f>"1. " &amp; data!$B$67</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G260)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -3601,7 +3601,7 @@
         <f>"2. " &amp; data!$B$74</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O19)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O16)</f>
       </c>
     </row>
     <row r="7">
@@ -3622,7 +3622,7 @@
         <f>'data'!$A$78</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O55)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O52)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3645,7 +3645,7 @@
         <f>"2. " &amp; data!$B$77</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O39)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O36)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3662,7 +3662,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O89)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O86)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3684,7 +3684,7 @@
         <f>"1. " &amp; data!$B$79</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O73)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O70)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3709,7 +3709,7 @@
         <f>"3. " &amp; data!$B$81</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O123)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O120)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3729,7 +3729,7 @@
         <f>'data'!$A$84</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O107)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O104)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3748,7 +3748,7 @@
         <f>"2. " &amp; data!$B$83</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O157)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O154)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3765,7 +3765,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O141)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O138)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3787,7 +3787,7 @@
         <f>"1. " &amp; data!$B$85</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O191)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O188)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3812,7 +3812,7 @@
         <f>"3. " &amp; data!$B$87</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O175)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O172)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3832,7 +3832,7 @@
         <f>'data'!$A$90</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O225)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O222)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -3851,7 +3851,7 @@
         <f>"2. " &amp; data!$B$89</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O209)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O206)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3872,7 +3872,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O259)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -3892,7 +3892,7 @@
         <f>"1. " &amp; data!$B$91</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O243)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O240)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -12119,7 +12119,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G39)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -12127,10 +12127,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G55)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G56)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -12138,7 +12138,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G22)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G18)</f>
       </c>
     </row>
     <row r="6">
@@ -12203,7 +12203,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G73)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -12211,10 +12211,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G89)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G86)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G90)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G87)</f>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -12222,7 +12222,7 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G72)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
       </c>
     </row>
     <row r="14">
@@ -12287,7 +12287,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G107)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G104)</f>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -12295,10 +12295,10 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G123)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G120)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G124)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G121)</f>
       </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -12306,7 +12306,7 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G106)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G103)</f>
       </c>
     </row>
     <row r="22">
@@ -12371,7 +12371,7 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G141)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G138)</f>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -12379,10 +12379,10 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G157)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G154)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G158)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G155)</f>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -12390,7 +12390,7 @@
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G140)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G137)</f>
       </c>
     </row>
     <row r="30">
@@ -12455,7 +12455,7 @@
     </row>
     <row r="36">
       <c r="A36" s="14" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G175)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G172)</f>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -12463,10 +12463,10 @@
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
       <c r="G36" s="14" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G191)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G188)</f>
       </c>
       <c r="I36" s="14" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G192)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G189)</f>
       </c>
       <c r="J36" s="18"/>
       <c r="K36" s="18"/>
@@ -12474,7 +12474,7 @@
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
       <c r="O36" s="14" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G174)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G171)</f>
       </c>
     </row>
     <row r="38">
@@ -12539,7 +12539,7 @@
     </row>
     <row r="44">
       <c r="A44" s="14" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G209)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G206)</f>
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
@@ -12547,10 +12547,10 @@
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="14" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G225)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G222)</f>
       </c>
       <c r="I44" s="14" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G226)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G223)</f>
       </c>
       <c r="J44" s="18"/>
       <c r="K44" s="18"/>
@@ -12558,7 +12558,7 @@
       <c r="M44" s="18"/>
       <c r="N44" s="18"/>
       <c r="O44" s="14" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G208)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G205)</f>
       </c>
     </row>
     <row r="46">
@@ -12623,7 +12623,7 @@
     </row>
     <row r="52">
       <c r="A52" s="14" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G243)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G240)</f>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -12631,10 +12631,10 @@
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G259)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
       </c>
       <c r="I52" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G260)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
       </c>
       <c r="J52" s="18"/>
       <c r="K52" s="18"/>
@@ -12642,7 +12642,7 @@
       <c r="M52" s="18"/>
       <c r="N52" s="18"/>
       <c r="O52" s="14" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G242)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G239)</f>
       </c>
     </row>
     <row r="54">
@@ -12707,7 +12707,7 @@
     </row>
     <row r="60">
       <c r="A60" s="14" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O56)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O53)</f>
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
@@ -12715,10 +12715,10 @@
       <c r="E60" s="18"/>
       <c r="F60" s="18"/>
       <c r="G60" s="14" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O20)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O17)</f>
       </c>
       <c r="I60" s="14" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O39)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O36)</f>
       </c>
       <c r="J60" s="18"/>
       <c r="K60" s="18"/>
@@ -12726,7 +12726,7 @@
       <c r="M60" s="18"/>
       <c r="N60" s="18"/>
       <c r="O60" s="14" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O55)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O52)</f>
       </c>
     </row>
     <row r="62">
@@ -12791,7 +12791,7 @@
     </row>
     <row r="68">
       <c r="A68" s="14" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O90)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O87)</f>
       </c>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -12799,10 +12799,10 @@
       <c r="E68" s="18"/>
       <c r="F68" s="18"/>
       <c r="G68" s="14" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O72)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O69)</f>
       </c>
       <c r="I68" s="14" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O73)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O70)</f>
       </c>
       <c r="J68" s="18"/>
       <c r="K68" s="18"/>
@@ -12810,7 +12810,7 @@
       <c r="M68" s="18"/>
       <c r="N68" s="18"/>
       <c r="O68" s="14" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O89)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O86)</f>
       </c>
     </row>
     <row r="70">
@@ -12875,7 +12875,7 @@
     </row>
     <row r="76">
       <c r="A76" s="14" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O124)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O121)</f>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -12883,10 +12883,10 @@
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
       <c r="G76" s="14" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O106)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O103)</f>
       </c>
       <c r="I76" s="14" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O107)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O104)</f>
       </c>
       <c r="J76" s="18"/>
       <c r="K76" s="18"/>
@@ -12894,7 +12894,7 @@
       <c r="M76" s="18"/>
       <c r="N76" s="18"/>
       <c r="O76" s="14" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O123)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O120)</f>
       </c>
     </row>
     <row r="78">
@@ -12959,7 +12959,7 @@
     </row>
     <row r="84">
       <c r="A84" s="14" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O158)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O155)</f>
       </c>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
@@ -12967,10 +12967,10 @@
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
       <c r="G84" s="14" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O140)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O137)</f>
       </c>
       <c r="I84" s="14" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O141)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O138)</f>
       </c>
       <c r="J84" s="18"/>
       <c r="K84" s="18"/>
@@ -12978,7 +12978,7 @@
       <c r="M84" s="18"/>
       <c r="N84" s="18"/>
       <c r="O84" s="14" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O157)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O154)</f>
       </c>
     </row>
     <row r="86">
@@ -13043,7 +13043,7 @@
     </row>
     <row r="92">
       <c r="A92" s="14" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O192)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O189)</f>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
@@ -13051,10 +13051,10 @@
       <c r="E92" s="18"/>
       <c r="F92" s="18"/>
       <c r="G92" s="14" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O174)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O171)</f>
       </c>
       <c r="I92" s="14" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O175)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O172)</f>
       </c>
       <c r="J92" s="18"/>
       <c r="K92" s="18"/>
@@ -13062,7 +13062,7 @@
       <c r="M92" s="18"/>
       <c r="N92" s="18"/>
       <c r="O92" s="14" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O191)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O188)</f>
       </c>
     </row>
     <row r="94">
@@ -13127,7 +13127,7 @@
     </row>
     <row r="100">
       <c r="A100" s="14" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O226)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O223)</f>
       </c>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
@@ -13135,10 +13135,10 @@
       <c r="E100" s="18"/>
       <c r="F100" s="18"/>
       <c r="G100" s="14" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O208)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O205)</f>
       </c>
       <c r="I100" s="14" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O209)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O206)</f>
       </c>
       <c r="J100" s="18"/>
       <c r="K100" s="18"/>
@@ -13146,7 +13146,7 @@
       <c r="M100" s="18"/>
       <c r="N100" s="18"/>
       <c r="O100" s="14" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O225)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O222)</f>
       </c>
     </row>
     <row r="102">
@@ -13211,7 +13211,7 @@
     </row>
     <row r="108">
       <c r="A108" s="14" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O260)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
       </c>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -13219,10 +13219,10 @@
       <c r="E108" s="18"/>
       <c r="F108" s="18"/>
       <c r="G108" s="14" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O242)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O239)</f>
       </c>
       <c r="I108" s="14" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O243)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O240)</f>
       </c>
       <c r="J108" s="18"/>
       <c r="K108" s="18"/>
@@ -13230,7 +13230,7 @@
       <c r="M108" s="18"/>
       <c r="N108" s="18"/>
       <c r="O108" s="14" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O259)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
       </c>
     </row>
     <row r="110">
@@ -13303,7 +13303,7 @@
       <c r="E121" s="18"/>
       <c r="F121" s="18"/>
       <c r="G121" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G21)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G17)</f>
       </c>
       <c r="I121" s="14" t="str">
         <f>CONCATENATE("M 15 ",O6)</f>
@@ -13314,7 +13314,7 @@
       <c r="M121" s="18"/>
       <c r="N121" s="18"/>
       <c r="O121" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G38)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
       </c>
     </row>
     <row r="123">
@@ -13639,7 +13639,7 @@
       <c r="E153" s="18"/>
       <c r="F153" s="18"/>
       <c r="G153" s="14" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O38)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O35)</f>
       </c>
       <c r="I153" s="14" t="str">
         <f>CONCATENATE("M 22 ",O62)</f>
@@ -13650,7 +13650,7 @@
       <c r="M153" s="18"/>
       <c r="N153" s="18"/>
       <c r="O153" s="14" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O19)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O16)</f>
       </c>
     </row>
     <row r="155">
@@ -14685,7 +14685,7 @@
         <f>"2. " &amp; data!$B$4</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G21)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G17)</f>
       </c>
     </row>
     <row r="7">
@@ -14706,7 +14706,7 @@
     <row r="9">
       <c r="A9" s="22"/>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G55)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -14729,7 +14729,7 @@
         <f>"1. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G39)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -14748,7 +14748,7 @@
         <f>"3. " &amp; data!$B$9</f>
       </c>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G89)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G86)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -14768,7 +14768,7 @@
         <f>'data'!$A$12</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G73)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -14793,7 +14793,7 @@
         <f>"2. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G123)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G120)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -14813,7 +14813,7 @@
     <row r="19">
       <c r="A19" s="22"/>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G107)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G104)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -14832,7 +14832,7 @@
         <f>"1. " &amp; data!$B$13</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G157)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G154)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -14851,7 +14851,7 @@
         <f>"3. " &amp; data!$B$15</f>
       </c>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G141)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G138)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -14871,7 +14871,7 @@
         <f>'data'!$A$18</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G191)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G188)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -14896,7 +14896,7 @@
         <f>"2. " &amp; data!$B$17</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G175)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G172)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -14916,7 +14916,7 @@
     <row r="29">
       <c r="A29" s="22"/>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G225)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G222)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -14935,7 +14935,7 @@
         <f>"1. " &amp; data!$B$19</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G209)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G206)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -14958,7 +14958,7 @@
         <f>"3. " &amp; data!$B$21</f>
       </c>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G259)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -14976,7 +14976,7 @@
         <f>'data'!$A$24</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G243)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G240)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -15076,7 +15076,7 @@
         <f>"2. " &amp; data!$B$29</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O38)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O35)</f>
       </c>
     </row>
     <row r="7">
@@ -15097,7 +15097,7 @@
         <f>'data'!$A$33</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O20)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O17)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -15120,7 +15120,7 @@
         <f>"2. " &amp; data!$B$32</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O56)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O53)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -15137,7 +15137,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O72)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O69)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -15159,7 +15159,7 @@
         <f>"1. " &amp; data!$B$34</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O90)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O87)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -15184,7 +15184,7 @@
         <f>"3. " &amp; data!$B$36</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O106)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O103)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -15204,7 +15204,7 @@
         <f>'data'!$A$39</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O124)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O121)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -15223,7 +15223,7 @@
         <f>"2. " &amp; data!$B$38</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O140)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O137)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -15240,7 +15240,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O158)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O155)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -15262,7 +15262,7 @@
         <f>"1. " &amp; data!$B$40</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O174)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O171)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -15287,7 +15287,7 @@
         <f>"3. " &amp; data!$B$42</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O192)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O189)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -15307,7 +15307,7 @@
         <f>'data'!$A$45</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O208)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O205)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -15326,7 +15326,7 @@
         <f>"2. " &amp; data!$B$44</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O226)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O223)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -15347,7 +15347,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O242)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O239)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -15367,7 +15367,7 @@
         <f>"1. " &amp; data!$B$46</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O260)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -6779,10 +6779,10 @@
         <f>RANK(AC10,$AC$10:$AC$12)+COUNTIF($AC$9:AC9,AC10)</f>
       </c>
       <c r="U10" t="str">
-        <f>=(B10*1000000)-(C10*10000)+(D10*100)+(E10*1)-(F10*0.01)</f>
+        <f>(B10*1000000)-(C10*10000)+(D10*100)+(E10*1)-(F10*0.01)</f>
       </c>
       <c r="AC10" t="str">
-        <f>=(J10*1000000)-(K10*10000)+(L10*100)+(M10*1)-(N10*0.01)</f>
+        <f>(J10*1000000)-(K10*10000)+(L10*100)+(M10*1)-(N10*0.01)</f>
       </c>
     </row>
     <row r="11">
@@ -6829,10 +6829,10 @@
         <f>RANK(AC11,$AC$10:$AC$12)+COUNTIF($AC$9:AC10,AC11)</f>
       </c>
       <c r="U11" t="str">
-        <f>=(B11*1000000)-(C11*10000)+(D11*100)+(E11*1)-(F11*0.01)</f>
+        <f>(B11*1000000)-(C11*10000)+(D11*100)+(E11*1)-(F11*0.01)</f>
       </c>
       <c r="AC11" t="str">
-        <f>=(J11*1000000)-(K11*10000)+(L11*100)+(M11*1)-(N11*0.01)</f>
+        <f>(J11*1000000)-(K11*10000)+(L11*100)+(M11*1)-(N11*0.01)</f>
       </c>
     </row>
     <row r="12">
@@ -6879,10 +6879,10 @@
         <f>RANK(AC12,$AC$10:$AC$12)+COUNTIF($AC$9:AC11,AC12)</f>
       </c>
       <c r="U12" t="str">
-        <f>=(B12*1000000)-(C12*10000)+(D12*100)+(E12*1)-(F12*0.01)</f>
+        <f>(B12*1000000)-(C12*10000)+(D12*100)+(E12*1)-(F12*0.01)</f>
       </c>
       <c r="AC12" t="str">
-        <f>=(J12*1000000)-(K12*10000)+(L12*100)+(M12*1)-(N12*0.01)</f>
+        <f>(J12*1000000)-(K12*10000)+(L12*100)+(M12*1)-(N12*0.01)</f>
       </c>
     </row>
     <row r="13">
@@ -6908,7 +6908,7 @@
         <f>RANK(U13,$U$10:$U$13)+COUNTIF($U$9:U12,U13)</f>
       </c>
       <c r="U13" t="str">
-        <f>=(B13*1000000)-(C13*10000)+(D13*100)+(E13*1)-(F13*0.01)</f>
+        <f>(B13*1000000)-(C13*10000)+(D13*100)+(E13*1)-(F13*0.01)</f>
       </c>
     </row>
     <row r="15">
@@ -7173,10 +7173,10 @@
         <f>RANK(AC29,$AC$29:$AC$31)+COUNTIF($AC$28:AC28,AC29)</f>
       </c>
       <c r="U29" t="str">
-        <f>=(B29*1000000)-(C29*10000)+(D29*100)+(E29*1)-(F29*0.01)</f>
+        <f>(B29*1000000)-(C29*10000)+(D29*100)+(E29*1)-(F29*0.01)</f>
       </c>
       <c r="AC29" t="str">
-        <f>=(J29*1000000)-(K29*10000)+(L29*100)+(M29*1)-(N29*0.01)</f>
+        <f>(J29*1000000)-(K29*10000)+(L29*100)+(M29*1)-(N29*0.01)</f>
       </c>
     </row>
     <row r="30">
@@ -7223,10 +7223,10 @@
         <f>RANK(AC30,$AC$29:$AC$31)+COUNTIF($AC$28:AC29,AC30)</f>
       </c>
       <c r="U30" t="str">
-        <f>=(B30*1000000)-(C30*10000)+(D30*100)+(E30*1)-(F30*0.01)</f>
+        <f>(B30*1000000)-(C30*10000)+(D30*100)+(E30*1)-(F30*0.01)</f>
       </c>
       <c r="AC30" t="str">
-        <f>=(J30*1000000)-(K30*10000)+(L30*100)+(M30*1)-(N30*0.01)</f>
+        <f>(J30*1000000)-(K30*10000)+(L30*100)+(M30*1)-(N30*0.01)</f>
       </c>
     </row>
     <row r="31">
@@ -7273,10 +7273,10 @@
         <f>RANK(AC31,$AC$29:$AC$31)+COUNTIF($AC$28:AC30,AC31)</f>
       </c>
       <c r="U31" t="str">
-        <f>=(B31*1000000)-(C31*10000)+(D31*100)+(E31*1)-(F31*0.01)</f>
+        <f>(B31*1000000)-(C31*10000)+(D31*100)+(E31*1)-(F31*0.01)</f>
       </c>
       <c r="AC31" t="str">
-        <f>=(J31*1000000)-(K31*10000)+(L31*100)+(M31*1)-(N31*0.01)</f>
+        <f>(J31*1000000)-(K31*10000)+(L31*100)+(M31*1)-(N31*0.01)</f>
       </c>
     </row>
     <row r="34">
@@ -7531,10 +7531,10 @@
         <f>RANK(AC46,$AC$46:$AC$48)+COUNTIF($AC$45:AC45,AC46)</f>
       </c>
       <c r="U46" t="str">
-        <f>=(B46*1000000)-(C46*10000)+(D46*100)+(E46*1)-(F46*0.01)</f>
+        <f>(B46*1000000)-(C46*10000)+(D46*100)+(E46*1)-(F46*0.01)</f>
       </c>
       <c r="AC46" t="str">
-        <f>=(J46*1000000)-(K46*10000)+(L46*100)+(M46*1)-(N46*0.01)</f>
+        <f>(J46*1000000)-(K46*10000)+(L46*100)+(M46*1)-(N46*0.01)</f>
       </c>
     </row>
     <row r="47">
@@ -7581,10 +7581,10 @@
         <f>RANK(AC47,$AC$46:$AC$48)+COUNTIF($AC$45:AC46,AC47)</f>
       </c>
       <c r="U47" t="str">
-        <f>=(B47*1000000)-(C47*10000)+(D47*100)+(E47*1)-(F47*0.01)</f>
+        <f>(B47*1000000)-(C47*10000)+(D47*100)+(E47*1)-(F47*0.01)</f>
       </c>
       <c r="AC47" t="str">
-        <f>=(J47*1000000)-(K47*10000)+(L47*100)+(M47*1)-(N47*0.01)</f>
+        <f>(J47*1000000)-(K47*10000)+(L47*100)+(M47*1)-(N47*0.01)</f>
       </c>
     </row>
     <row r="48">
@@ -7631,10 +7631,10 @@
         <f>RANK(AC48,$AC$46:$AC$48)+COUNTIF($AC$45:AC47,AC48)</f>
       </c>
       <c r="U48" t="str">
-        <f>=(B48*1000000)-(C48*10000)+(D48*100)+(E48*1)-(F48*0.01)</f>
+        <f>(B48*1000000)-(C48*10000)+(D48*100)+(E48*1)-(F48*0.01)</f>
       </c>
       <c r="AC48" t="str">
-        <f>=(J48*1000000)-(K48*10000)+(L48*100)+(M48*1)-(N48*0.01)</f>
+        <f>(J48*1000000)-(K48*10000)+(L48*100)+(M48*1)-(N48*0.01)</f>
       </c>
     </row>
     <row r="51">
@@ -7889,10 +7889,10 @@
         <f>RANK(AC63,$AC$63:$AC$65)+COUNTIF($AC$62:AC62,AC63)</f>
       </c>
       <c r="U63" t="str">
-        <f>=(B63*1000000)-(C63*10000)+(D63*100)+(E63*1)-(F63*0.01)</f>
+        <f>(B63*1000000)-(C63*10000)+(D63*100)+(E63*1)-(F63*0.01)</f>
       </c>
       <c r="AC63" t="str">
-        <f>=(J63*1000000)-(K63*10000)+(L63*100)+(M63*1)-(N63*0.01)</f>
+        <f>(J63*1000000)-(K63*10000)+(L63*100)+(M63*1)-(N63*0.01)</f>
       </c>
     </row>
     <row r="64">
@@ -7939,10 +7939,10 @@
         <f>RANK(AC64,$AC$63:$AC$65)+COUNTIF($AC$62:AC63,AC64)</f>
       </c>
       <c r="U64" t="str">
-        <f>=(B64*1000000)-(C64*10000)+(D64*100)+(E64*1)-(F64*0.01)</f>
+        <f>(B64*1000000)-(C64*10000)+(D64*100)+(E64*1)-(F64*0.01)</f>
       </c>
       <c r="AC64" t="str">
-        <f>=(J64*1000000)-(K64*10000)+(L64*100)+(M64*1)-(N64*0.01)</f>
+        <f>(J64*1000000)-(K64*10000)+(L64*100)+(M64*1)-(N64*0.01)</f>
       </c>
     </row>
     <row r="65">
@@ -7989,10 +7989,10 @@
         <f>RANK(AC65,$AC$63:$AC$65)+COUNTIF($AC$62:AC64,AC65)</f>
       </c>
       <c r="U65" t="str">
-        <f>=(B65*1000000)-(C65*10000)+(D65*100)+(E65*1)-(F65*0.01)</f>
+        <f>(B65*1000000)-(C65*10000)+(D65*100)+(E65*1)-(F65*0.01)</f>
       </c>
       <c r="AC65" t="str">
-        <f>=(J65*1000000)-(K65*10000)+(L65*100)+(M65*1)-(N65*0.01)</f>
+        <f>(J65*1000000)-(K65*10000)+(L65*100)+(M65*1)-(N65*0.01)</f>
       </c>
     </row>
     <row r="68">
@@ -8247,10 +8247,10 @@
         <f>RANK(AC80,$AC$80:$AC$82)+COUNTIF($AC$79:AC79,AC80)</f>
       </c>
       <c r="U80" t="str">
-        <f>=(B80*1000000)-(C80*10000)+(D80*100)+(E80*1)-(F80*0.01)</f>
+        <f>(B80*1000000)-(C80*10000)+(D80*100)+(E80*1)-(F80*0.01)</f>
       </c>
       <c r="AC80" t="str">
-        <f>=(J80*1000000)-(K80*10000)+(L80*100)+(M80*1)-(N80*0.01)</f>
+        <f>(J80*1000000)-(K80*10000)+(L80*100)+(M80*1)-(N80*0.01)</f>
       </c>
     </row>
     <row r="81">
@@ -8297,10 +8297,10 @@
         <f>RANK(AC81,$AC$80:$AC$82)+COUNTIF($AC$79:AC80,AC81)</f>
       </c>
       <c r="U81" t="str">
-        <f>=(B81*1000000)-(C81*10000)+(D81*100)+(E81*1)-(F81*0.01)</f>
+        <f>(B81*1000000)-(C81*10000)+(D81*100)+(E81*1)-(F81*0.01)</f>
       </c>
       <c r="AC81" t="str">
-        <f>=(J81*1000000)-(K81*10000)+(L81*100)+(M81*1)-(N81*0.01)</f>
+        <f>(J81*1000000)-(K81*10000)+(L81*100)+(M81*1)-(N81*0.01)</f>
       </c>
     </row>
     <row r="82">
@@ -8347,10 +8347,10 @@
         <f>RANK(AC82,$AC$80:$AC$82)+COUNTIF($AC$79:AC81,AC82)</f>
       </c>
       <c r="U82" t="str">
-        <f>=(B82*1000000)-(C82*10000)+(D82*100)+(E82*1)-(F82*0.01)</f>
+        <f>(B82*1000000)-(C82*10000)+(D82*100)+(E82*1)-(F82*0.01)</f>
       </c>
       <c r="AC82" t="str">
-        <f>=(J82*1000000)-(K82*10000)+(L82*100)+(M82*1)-(N82*0.01)</f>
+        <f>(J82*1000000)-(K82*10000)+(L82*100)+(M82*1)-(N82*0.01)</f>
       </c>
     </row>
     <row r="85">
@@ -8605,10 +8605,10 @@
         <f>RANK(AC97,$AC$97:$AC$99)+COUNTIF($AC$96:AC96,AC97)</f>
       </c>
       <c r="U97" t="str">
-        <f>=(B97*1000000)-(C97*10000)+(D97*100)+(E97*1)-(F97*0.01)</f>
+        <f>(B97*1000000)-(C97*10000)+(D97*100)+(E97*1)-(F97*0.01)</f>
       </c>
       <c r="AC97" t="str">
-        <f>=(J97*1000000)-(K97*10000)+(L97*100)+(M97*1)-(N97*0.01)</f>
+        <f>(J97*1000000)-(K97*10000)+(L97*100)+(M97*1)-(N97*0.01)</f>
       </c>
     </row>
     <row r="98">
@@ -8655,10 +8655,10 @@
         <f>RANK(AC98,$AC$97:$AC$99)+COUNTIF($AC$96:AC97,AC98)</f>
       </c>
       <c r="U98" t="str">
-        <f>=(B98*1000000)-(C98*10000)+(D98*100)+(E98*1)-(F98*0.01)</f>
+        <f>(B98*1000000)-(C98*10000)+(D98*100)+(E98*1)-(F98*0.01)</f>
       </c>
       <c r="AC98" t="str">
-        <f>=(J98*1000000)-(K98*10000)+(L98*100)+(M98*1)-(N98*0.01)</f>
+        <f>(J98*1000000)-(K98*10000)+(L98*100)+(M98*1)-(N98*0.01)</f>
       </c>
     </row>
     <row r="99">
@@ -8705,10 +8705,10 @@
         <f>RANK(AC99,$AC$97:$AC$99)+COUNTIF($AC$96:AC98,AC99)</f>
       </c>
       <c r="U99" t="str">
-        <f>=(B99*1000000)-(C99*10000)+(D99*100)+(E99*1)-(F99*0.01)</f>
+        <f>(B99*1000000)-(C99*10000)+(D99*100)+(E99*1)-(F99*0.01)</f>
       </c>
       <c r="AC99" t="str">
-        <f>=(J99*1000000)-(K99*10000)+(L99*100)+(M99*1)-(N99*0.01)</f>
+        <f>(J99*1000000)-(K99*10000)+(L99*100)+(M99*1)-(N99*0.01)</f>
       </c>
     </row>
     <row r="102">
@@ -8963,10 +8963,10 @@
         <f>RANK(AC114,$AC$114:$AC$116)+COUNTIF($AC$113:AC113,AC114)</f>
       </c>
       <c r="U114" t="str">
-        <f>=(B114*1000000)-(C114*10000)+(D114*100)+(E114*1)-(F114*0.01)</f>
+        <f>(B114*1000000)-(C114*10000)+(D114*100)+(E114*1)-(F114*0.01)</f>
       </c>
       <c r="AC114" t="str">
-        <f>=(J114*1000000)-(K114*10000)+(L114*100)+(M114*1)-(N114*0.01)</f>
+        <f>(J114*1000000)-(K114*10000)+(L114*100)+(M114*1)-(N114*0.01)</f>
       </c>
     </row>
     <row r="115">
@@ -9013,10 +9013,10 @@
         <f>RANK(AC115,$AC$114:$AC$116)+COUNTIF($AC$113:AC114,AC115)</f>
       </c>
       <c r="U115" t="str">
-        <f>=(B115*1000000)-(C115*10000)+(D115*100)+(E115*1)-(F115*0.01)</f>
+        <f>(B115*1000000)-(C115*10000)+(D115*100)+(E115*1)-(F115*0.01)</f>
       </c>
       <c r="AC115" t="str">
-        <f>=(J115*1000000)-(K115*10000)+(L115*100)+(M115*1)-(N115*0.01)</f>
+        <f>(J115*1000000)-(K115*10000)+(L115*100)+(M115*1)-(N115*0.01)</f>
       </c>
     </row>
     <row r="116">
@@ -9063,10 +9063,10 @@
         <f>RANK(AC116,$AC$114:$AC$116)+COUNTIF($AC$113:AC115,AC116)</f>
       </c>
       <c r="U116" t="str">
-        <f>=(B116*1000000)-(C116*10000)+(D116*100)+(E116*1)-(F116*0.01)</f>
+        <f>(B116*1000000)-(C116*10000)+(D116*100)+(E116*1)-(F116*0.01)</f>
       </c>
       <c r="AC116" t="str">
-        <f>=(J116*1000000)-(K116*10000)+(L116*100)+(M116*1)-(N116*0.01)</f>
+        <f>(J116*1000000)-(K116*10000)+(L116*100)+(M116*1)-(N116*0.01)</f>
       </c>
     </row>
     <row r="119">
@@ -9321,10 +9321,10 @@
         <f>RANK(AC131,$AC$131:$AC$133)+COUNTIF($AC$130:AC130,AC131)</f>
       </c>
       <c r="U131" t="str">
-        <f>=(B131*1000000)-(C131*10000)+(D131*100)+(E131*1)-(F131*0.01)</f>
+        <f>(B131*1000000)-(C131*10000)+(D131*100)+(E131*1)-(F131*0.01)</f>
       </c>
       <c r="AC131" t="str">
-        <f>=(J131*1000000)-(K131*10000)+(L131*100)+(M131*1)-(N131*0.01)</f>
+        <f>(J131*1000000)-(K131*10000)+(L131*100)+(M131*1)-(N131*0.01)</f>
       </c>
     </row>
     <row r="132">
@@ -9371,10 +9371,10 @@
         <f>RANK(AC132,$AC$131:$AC$133)+COUNTIF($AC$130:AC131,AC132)</f>
       </c>
       <c r="U132" t="str">
-        <f>=(B132*1000000)-(C132*10000)+(D132*100)+(E132*1)-(F132*0.01)</f>
+        <f>(B132*1000000)-(C132*10000)+(D132*100)+(E132*1)-(F132*0.01)</f>
       </c>
       <c r="AC132" t="str">
-        <f>=(J132*1000000)-(K132*10000)+(L132*100)+(M132*1)-(N132*0.01)</f>
+        <f>(J132*1000000)-(K132*10000)+(L132*100)+(M132*1)-(N132*0.01)</f>
       </c>
     </row>
     <row r="133">
@@ -9421,10 +9421,10 @@
         <f>RANK(AC133,$AC$131:$AC$133)+COUNTIF($AC$130:AC132,AC133)</f>
       </c>
       <c r="U133" t="str">
-        <f>=(B133*1000000)-(C133*10000)+(D133*100)+(E133*1)-(F133*0.01)</f>
+        <f>(B133*1000000)-(C133*10000)+(D133*100)+(E133*1)-(F133*0.01)</f>
       </c>
       <c r="AC133" t="str">
-        <f>=(J133*1000000)-(K133*10000)+(L133*100)+(M133*1)-(N133*0.01)</f>
+        <f>(J133*1000000)-(K133*10000)+(L133*100)+(M133*1)-(N133*0.01)</f>
       </c>
     </row>
     <row r="136">
@@ -9679,10 +9679,10 @@
         <f>RANK(AC148,$AC$148:$AC$150)+COUNTIF($AC$147:AC147,AC148)</f>
       </c>
       <c r="U148" t="str">
-        <f>=(B148*1000000)-(C148*10000)+(D148*100)+(E148*1)-(F148*0.01)</f>
+        <f>(B148*1000000)-(C148*10000)+(D148*100)+(E148*1)-(F148*0.01)</f>
       </c>
       <c r="AC148" t="str">
-        <f>=(J148*1000000)-(K148*10000)+(L148*100)+(M148*1)-(N148*0.01)</f>
+        <f>(J148*1000000)-(K148*10000)+(L148*100)+(M148*1)-(N148*0.01)</f>
       </c>
     </row>
     <row r="149">
@@ -9729,10 +9729,10 @@
         <f>RANK(AC149,$AC$148:$AC$150)+COUNTIF($AC$147:AC148,AC149)</f>
       </c>
       <c r="U149" t="str">
-        <f>=(B149*1000000)-(C149*10000)+(D149*100)+(E149*1)-(F149*0.01)</f>
+        <f>(B149*1000000)-(C149*10000)+(D149*100)+(E149*1)-(F149*0.01)</f>
       </c>
       <c r="AC149" t="str">
-        <f>=(J149*1000000)-(K149*10000)+(L149*100)+(M149*1)-(N149*0.01)</f>
+        <f>(J149*1000000)-(K149*10000)+(L149*100)+(M149*1)-(N149*0.01)</f>
       </c>
     </row>
     <row r="150">
@@ -9779,10 +9779,10 @@
         <f>RANK(AC150,$AC$148:$AC$150)+COUNTIF($AC$147:AC149,AC150)</f>
       </c>
       <c r="U150" t="str">
-        <f>=(B150*1000000)-(C150*10000)+(D150*100)+(E150*1)-(F150*0.01)</f>
+        <f>(B150*1000000)-(C150*10000)+(D150*100)+(E150*1)-(F150*0.01)</f>
       </c>
       <c r="AC150" t="str">
-        <f>=(J150*1000000)-(K150*10000)+(L150*100)+(M150*1)-(N150*0.01)</f>
+        <f>(J150*1000000)-(K150*10000)+(L150*100)+(M150*1)-(N150*0.01)</f>
       </c>
     </row>
     <row r="153">
@@ -10037,10 +10037,10 @@
         <f>RANK(AC165,$AC$165:$AC$167)+COUNTIF($AC$164:AC164,AC165)</f>
       </c>
       <c r="U165" t="str">
-        <f>=(B165*1000000)-(C165*10000)+(D165*100)+(E165*1)-(F165*0.01)</f>
+        <f>(B165*1000000)-(C165*10000)+(D165*100)+(E165*1)-(F165*0.01)</f>
       </c>
       <c r="AC165" t="str">
-        <f>=(J165*1000000)-(K165*10000)+(L165*100)+(M165*1)-(N165*0.01)</f>
+        <f>(J165*1000000)-(K165*10000)+(L165*100)+(M165*1)-(N165*0.01)</f>
       </c>
     </row>
     <row r="166">
@@ -10087,10 +10087,10 @@
         <f>RANK(AC166,$AC$165:$AC$167)+COUNTIF($AC$164:AC165,AC166)</f>
       </c>
       <c r="U166" t="str">
-        <f>=(B166*1000000)-(C166*10000)+(D166*100)+(E166*1)-(F166*0.01)</f>
+        <f>(B166*1000000)-(C166*10000)+(D166*100)+(E166*1)-(F166*0.01)</f>
       </c>
       <c r="AC166" t="str">
-        <f>=(J166*1000000)-(K166*10000)+(L166*100)+(M166*1)-(N166*0.01)</f>
+        <f>(J166*1000000)-(K166*10000)+(L166*100)+(M166*1)-(N166*0.01)</f>
       </c>
     </row>
     <row r="167">
@@ -10137,10 +10137,10 @@
         <f>RANK(AC167,$AC$165:$AC$167)+COUNTIF($AC$164:AC166,AC167)</f>
       </c>
       <c r="U167" t="str">
-        <f>=(B167*1000000)-(C167*10000)+(D167*100)+(E167*1)-(F167*0.01)</f>
+        <f>(B167*1000000)-(C167*10000)+(D167*100)+(E167*1)-(F167*0.01)</f>
       </c>
       <c r="AC167" t="str">
-        <f>=(J167*1000000)-(K167*10000)+(L167*100)+(M167*1)-(N167*0.01)</f>
+        <f>(J167*1000000)-(K167*10000)+(L167*100)+(M167*1)-(N167*0.01)</f>
       </c>
     </row>
     <row r="170">
@@ -10395,10 +10395,10 @@
         <f>RANK(AC182,$AC$182:$AC$184)+COUNTIF($AC$181:AC181,AC182)</f>
       </c>
       <c r="U182" t="str">
-        <f>=(B182*1000000)-(C182*10000)+(D182*100)+(E182*1)-(F182*0.01)</f>
+        <f>(B182*1000000)-(C182*10000)+(D182*100)+(E182*1)-(F182*0.01)</f>
       </c>
       <c r="AC182" t="str">
-        <f>=(J182*1000000)-(K182*10000)+(L182*100)+(M182*1)-(N182*0.01)</f>
+        <f>(J182*1000000)-(K182*10000)+(L182*100)+(M182*1)-(N182*0.01)</f>
       </c>
     </row>
     <row r="183">
@@ -10445,10 +10445,10 @@
         <f>RANK(AC183,$AC$182:$AC$184)+COUNTIF($AC$181:AC182,AC183)</f>
       </c>
       <c r="U183" t="str">
-        <f>=(B183*1000000)-(C183*10000)+(D183*100)+(E183*1)-(F183*0.01)</f>
+        <f>(B183*1000000)-(C183*10000)+(D183*100)+(E183*1)-(F183*0.01)</f>
       </c>
       <c r="AC183" t="str">
-        <f>=(J183*1000000)-(K183*10000)+(L183*100)+(M183*1)-(N183*0.01)</f>
+        <f>(J183*1000000)-(K183*10000)+(L183*100)+(M183*1)-(N183*0.01)</f>
       </c>
     </row>
     <row r="184">
@@ -10495,10 +10495,10 @@
         <f>RANK(AC184,$AC$182:$AC$184)+COUNTIF($AC$181:AC183,AC184)</f>
       </c>
       <c r="U184" t="str">
-        <f>=(B184*1000000)-(C184*10000)+(D184*100)+(E184*1)-(F184*0.01)</f>
+        <f>(B184*1000000)-(C184*10000)+(D184*100)+(E184*1)-(F184*0.01)</f>
       </c>
       <c r="AC184" t="str">
-        <f>=(J184*1000000)-(K184*10000)+(L184*100)+(M184*1)-(N184*0.01)</f>
+        <f>(J184*1000000)-(K184*10000)+(L184*100)+(M184*1)-(N184*0.01)</f>
       </c>
     </row>
     <row r="187">
@@ -10753,10 +10753,10 @@
         <f>RANK(AC199,$AC$199:$AC$201)+COUNTIF($AC$198:AC198,AC199)</f>
       </c>
       <c r="U199" t="str">
-        <f>=(B199*1000000)-(C199*10000)+(D199*100)+(E199*1)-(F199*0.01)</f>
+        <f>(B199*1000000)-(C199*10000)+(D199*100)+(E199*1)-(F199*0.01)</f>
       </c>
       <c r="AC199" t="str">
-        <f>=(J199*1000000)-(K199*10000)+(L199*100)+(M199*1)-(N199*0.01)</f>
+        <f>(J199*1000000)-(K199*10000)+(L199*100)+(M199*1)-(N199*0.01)</f>
       </c>
     </row>
     <row r="200">
@@ -10803,10 +10803,10 @@
         <f>RANK(AC200,$AC$199:$AC$201)+COUNTIF($AC$198:AC199,AC200)</f>
       </c>
       <c r="U200" t="str">
-        <f>=(B200*1000000)-(C200*10000)+(D200*100)+(E200*1)-(F200*0.01)</f>
+        <f>(B200*1000000)-(C200*10000)+(D200*100)+(E200*1)-(F200*0.01)</f>
       </c>
       <c r="AC200" t="str">
-        <f>=(J200*1000000)-(K200*10000)+(L200*100)+(M200*1)-(N200*0.01)</f>
+        <f>(J200*1000000)-(K200*10000)+(L200*100)+(M200*1)-(N200*0.01)</f>
       </c>
     </row>
     <row r="201">
@@ -10853,10 +10853,10 @@
         <f>RANK(AC201,$AC$199:$AC$201)+COUNTIF($AC$198:AC200,AC201)</f>
       </c>
       <c r="U201" t="str">
-        <f>=(B201*1000000)-(C201*10000)+(D201*100)+(E201*1)-(F201*0.01)</f>
+        <f>(B201*1000000)-(C201*10000)+(D201*100)+(E201*1)-(F201*0.01)</f>
       </c>
       <c r="AC201" t="str">
-        <f>=(J201*1000000)-(K201*10000)+(L201*100)+(M201*1)-(N201*0.01)</f>
+        <f>(J201*1000000)-(K201*10000)+(L201*100)+(M201*1)-(N201*0.01)</f>
       </c>
     </row>
     <row r="204">
@@ -11111,10 +11111,10 @@
         <f>RANK(AC216,$AC$216:$AC$218)+COUNTIF($AC$215:AC215,AC216)</f>
       </c>
       <c r="U216" t="str">
-        <f>=(B216*1000000)-(C216*10000)+(D216*100)+(E216*1)-(F216*0.01)</f>
+        <f>(B216*1000000)-(C216*10000)+(D216*100)+(E216*1)-(F216*0.01)</f>
       </c>
       <c r="AC216" t="str">
-        <f>=(J216*1000000)-(K216*10000)+(L216*100)+(M216*1)-(N216*0.01)</f>
+        <f>(J216*1000000)-(K216*10000)+(L216*100)+(M216*1)-(N216*0.01)</f>
       </c>
     </row>
     <row r="217">
@@ -11161,10 +11161,10 @@
         <f>RANK(AC217,$AC$216:$AC$218)+COUNTIF($AC$215:AC216,AC217)</f>
       </c>
       <c r="U217" t="str">
-        <f>=(B217*1000000)-(C217*10000)+(D217*100)+(E217*1)-(F217*0.01)</f>
+        <f>(B217*1000000)-(C217*10000)+(D217*100)+(E217*1)-(F217*0.01)</f>
       </c>
       <c r="AC217" t="str">
-        <f>=(J217*1000000)-(K217*10000)+(L217*100)+(M217*1)-(N217*0.01)</f>
+        <f>(J217*1000000)-(K217*10000)+(L217*100)+(M217*1)-(N217*0.01)</f>
       </c>
     </row>
     <row r="218">
@@ -11211,10 +11211,10 @@
         <f>RANK(AC218,$AC$216:$AC$218)+COUNTIF($AC$215:AC217,AC218)</f>
       </c>
       <c r="U218" t="str">
-        <f>=(B218*1000000)-(C218*10000)+(D218*100)+(E218*1)-(F218*0.01)</f>
+        <f>(B218*1000000)-(C218*10000)+(D218*100)+(E218*1)-(F218*0.01)</f>
       </c>
       <c r="AC218" t="str">
-        <f>=(J218*1000000)-(K218*10000)+(L218*100)+(M218*1)-(N218*0.01)</f>
+        <f>(J218*1000000)-(K218*10000)+(L218*100)+(M218*1)-(N218*0.01)</f>
       </c>
     </row>
     <row r="221">
@@ -11469,10 +11469,10 @@
         <f>RANK(AC233,$AC$233:$AC$235)+COUNTIF($AC$232:AC232,AC233)</f>
       </c>
       <c r="U233" t="str">
-        <f>=(B233*1000000)-(C233*10000)+(D233*100)+(E233*1)-(F233*0.01)</f>
+        <f>(B233*1000000)-(C233*10000)+(D233*100)+(E233*1)-(F233*0.01)</f>
       </c>
       <c r="AC233" t="str">
-        <f>=(J233*1000000)-(K233*10000)+(L233*100)+(M233*1)-(N233*0.01)</f>
+        <f>(J233*1000000)-(K233*10000)+(L233*100)+(M233*1)-(N233*0.01)</f>
       </c>
     </row>
     <row r="234">
@@ -11519,10 +11519,10 @@
         <f>RANK(AC234,$AC$233:$AC$235)+COUNTIF($AC$232:AC233,AC234)</f>
       </c>
       <c r="U234" t="str">
-        <f>=(B234*1000000)-(C234*10000)+(D234*100)+(E234*1)-(F234*0.01)</f>
+        <f>(B234*1000000)-(C234*10000)+(D234*100)+(E234*1)-(F234*0.01)</f>
       </c>
       <c r="AC234" t="str">
-        <f>=(J234*1000000)-(K234*10000)+(L234*100)+(M234*1)-(N234*0.01)</f>
+        <f>(J234*1000000)-(K234*10000)+(L234*100)+(M234*1)-(N234*0.01)</f>
       </c>
     </row>
     <row r="235">
@@ -11569,10 +11569,10 @@
         <f>RANK(AC235,$AC$233:$AC$235)+COUNTIF($AC$232:AC234,AC235)</f>
       </c>
       <c r="U235" t="str">
-        <f>=(B235*1000000)-(C235*10000)+(D235*100)+(E235*1)-(F235*0.01)</f>
+        <f>(B235*1000000)-(C235*10000)+(D235*100)+(E235*1)-(F235*0.01)</f>
       </c>
       <c r="AC235" t="str">
-        <f>=(J235*1000000)-(K235*10000)+(L235*100)+(M235*1)-(N235*0.01)</f>
+        <f>(J235*1000000)-(K235*10000)+(L235*100)+(M235*1)-(N235*0.01)</f>
       </c>
     </row>
     <row r="238">
@@ -11827,10 +11827,10 @@
         <f>RANK(AC250,$AC$250:$AC$252)+COUNTIF($AC$249:AC249,AC250)</f>
       </c>
       <c r="U250" t="str">
-        <f>=(B250*1000000)-(C250*10000)+(D250*100)+(E250*1)-(F250*0.01)</f>
+        <f>(B250*1000000)-(C250*10000)+(D250*100)+(E250*1)-(F250*0.01)</f>
       </c>
       <c r="AC250" t="str">
-        <f>=(J250*1000000)-(K250*10000)+(L250*100)+(M250*1)-(N250*0.01)</f>
+        <f>(J250*1000000)-(K250*10000)+(L250*100)+(M250*1)-(N250*0.01)</f>
       </c>
     </row>
     <row r="251">
@@ -11877,10 +11877,10 @@
         <f>RANK(AC251,$AC$250:$AC$252)+COUNTIF($AC$249:AC250,AC251)</f>
       </c>
       <c r="U251" t="str">
-        <f>=(B251*1000000)-(C251*10000)+(D251*100)+(E251*1)-(F251*0.01)</f>
+        <f>(B251*1000000)-(C251*10000)+(D251*100)+(E251*1)-(F251*0.01)</f>
       </c>
       <c r="AC251" t="str">
-        <f>=(J251*1000000)-(K251*10000)+(L251*100)+(M251*1)-(N251*0.01)</f>
+        <f>(J251*1000000)-(K251*10000)+(L251*100)+(M251*1)-(N251*0.01)</f>
       </c>
     </row>
     <row r="252">
@@ -11927,10 +11927,10 @@
         <f>RANK(AC252,$AC$250:$AC$252)+COUNTIF($AC$249:AC251,AC252)</f>
       </c>
       <c r="U252" t="str">
-        <f>=(B252*1000000)-(C252*10000)+(D252*100)+(E252*1)-(F252*0.01)</f>
+        <f>(B252*1000000)-(C252*10000)+(D252*100)+(E252*1)-(F252*0.01)</f>
       </c>
       <c r="AC252" t="str">
-        <f>=(J252*1000000)-(K252*10000)+(L252*100)+(M252*1)-(N252*0.01)</f>
+        <f>(J252*1000000)-(K252*10000)+(L252*100)+(M252*1)-(N252*0.01)</f>
       </c>
     </row>
     <row r="255">

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -1361,7 +1361,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="150"/>
+      <sz val="200"/>
     </font>
   </fonts>
   <fills count="6">
@@ -4721,912 +4721,912 @@
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
-    <row r="1" ht="390" customHeight="true">
+    <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="2" ht="390" customHeight="true">
+    <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="3" ht="390" customHeight="true">
+    <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="4" ht="390" customHeight="true">
+    <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="5" ht="390" customHeight="true">
+    <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="6" ht="390" customHeight="true">
+    <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="7" ht="390" customHeight="true">
+    <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="8" ht="390" customHeight="true">
+    <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="9" ht="390" customHeight="true">
+    <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="10" ht="390" customHeight="true">
+    <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="11" ht="390" customHeight="true">
+    <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="12" ht="390" customHeight="true">
+    <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="13" ht="390" customHeight="true">
+    <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="14" ht="390" customHeight="true">
+    <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="15" ht="390" customHeight="true">
+    <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="16" ht="390" customHeight="true">
+    <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="17" ht="390" customHeight="true">
+    <row r="17" ht="409" customHeight="true">
       <c r="A17" s="30" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="18" ht="390" customHeight="true">
+    <row r="18" ht="409" customHeight="true">
       <c r="A18" s="30" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="19" ht="390" customHeight="true">
+    <row r="19" ht="409" customHeight="true">
       <c r="A19" s="30" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="20" ht="390" customHeight="true">
+    <row r="20" ht="409" customHeight="true">
       <c r="A20" s="30" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="21" ht="390" customHeight="true">
+    <row r="21" ht="409" customHeight="true">
       <c r="A21" s="30" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="22" ht="390" customHeight="true">
+    <row r="22" ht="409" customHeight="true">
       <c r="A22" s="30" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="23" ht="390" customHeight="true">
+    <row r="23" ht="409" customHeight="true">
       <c r="A23" s="30" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="24" ht="390" customHeight="true">
+    <row r="24" ht="409" customHeight="true">
       <c r="A24" s="30" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="25" ht="390" customHeight="true">
+    <row r="25" ht="409" customHeight="true">
       <c r="A25" s="30" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="26" ht="390" customHeight="true">
+    <row r="26" ht="409" customHeight="true">
       <c r="A26" s="30" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="27" ht="390" customHeight="true">
+    <row r="27" ht="409" customHeight="true">
       <c r="A27" s="30" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="28" ht="390" customHeight="true">
+    <row r="28" ht="409" customHeight="true">
       <c r="A28" s="30" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="29" ht="390" customHeight="true">
+    <row r="29" ht="409" customHeight="true">
       <c r="A29" s="30" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="30" ht="390" customHeight="true">
+    <row r="30" ht="409" customHeight="true">
       <c r="A30" s="30" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="31" ht="390" customHeight="true">
+    <row r="31" ht="409" customHeight="true">
       <c r="A31" s="30" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="32" ht="390" customHeight="true">
+    <row r="32" ht="409" customHeight="true">
       <c r="A32" s="30" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="33" ht="390" customHeight="true">
+    <row r="33" ht="409" customHeight="true">
       <c r="A33" s="30" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="34" ht="390" customHeight="true">
+    <row r="34" ht="409" customHeight="true">
       <c r="A34" s="30" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="35" ht="390" customHeight="true">
+    <row r="35" ht="409" customHeight="true">
       <c r="A35" s="30" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="36" ht="390" customHeight="true">
+    <row r="36" ht="409" customHeight="true">
       <c r="A36" s="30" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="37" ht="390" customHeight="true">
+    <row r="37" ht="409" customHeight="true">
       <c r="A37" s="30" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="38" ht="390" customHeight="true">
+    <row r="38" ht="409" customHeight="true">
       <c r="A38" s="30" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="39" ht="390" customHeight="true">
+    <row r="39" ht="409" customHeight="true">
       <c r="A39" s="30" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="40" ht="390" customHeight="true">
+    <row r="40" ht="409" customHeight="true">
       <c r="A40" s="30" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="41" ht="390" customHeight="true">
+    <row r="41" ht="409" customHeight="true">
       <c r="A41" s="30" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="42" ht="390" customHeight="true">
+    <row r="42" ht="409" customHeight="true">
       <c r="A42" s="30" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="43" ht="390" customHeight="true">
+    <row r="43" ht="409" customHeight="true">
       <c r="A43" s="30" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="44" ht="390" customHeight="true">
+    <row r="44" ht="409" customHeight="true">
       <c r="A44" s="30" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="45" ht="390" customHeight="true">
+    <row r="45" ht="409" customHeight="true">
       <c r="A45" s="30" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="46" ht="390" customHeight="true">
+    <row r="46" ht="409" customHeight="true">
       <c r="A46" s="30" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="47" ht="390" customHeight="true">
+    <row r="47" ht="409" customHeight="true">
       <c r="A47" s="30" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="48" ht="390" customHeight="true">
+    <row r="48" ht="409" customHeight="true">
       <c r="A48" s="30" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="49" ht="390" customHeight="true">
+    <row r="49" ht="409" customHeight="true">
       <c r="A49" s="30" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="50" ht="390" customHeight="true">
+    <row r="50" ht="409" customHeight="true">
       <c r="A50" s="30" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="51" ht="390" customHeight="true">
+    <row r="51" ht="409" customHeight="true">
       <c r="A51" s="30" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="52" ht="390" customHeight="true">
+    <row r="52" ht="409" customHeight="true">
       <c r="A52" s="30" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="53" ht="390" customHeight="true">
+    <row r="53" ht="409" customHeight="true">
       <c r="A53" s="30" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="54" ht="390" customHeight="true">
+    <row r="54" ht="409" customHeight="true">
       <c r="A54" s="30" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="55" ht="390" customHeight="true">
+    <row r="55" ht="409" customHeight="true">
       <c r="A55" s="30" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="56" ht="390" customHeight="true">
+    <row r="56" ht="409" customHeight="true">
       <c r="A56" s="30" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="57" ht="390" customHeight="true">
+    <row r="57" ht="409" customHeight="true">
       <c r="A57" s="30" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="58" ht="390" customHeight="true">
+    <row r="58" ht="409" customHeight="true">
       <c r="A58" s="30" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="59" ht="390" customHeight="true">
+    <row r="59" ht="409" customHeight="true">
       <c r="A59" s="30" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="60" ht="390" customHeight="true">
+    <row r="60" ht="409" customHeight="true">
       <c r="A60" s="30" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="61" ht="390" customHeight="true">
+    <row r="61" ht="409" customHeight="true">
       <c r="A61" s="30" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="62" ht="390" customHeight="true">
+    <row r="62" ht="409" customHeight="true">
       <c r="A62" s="30" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="63" ht="390" customHeight="true">
+    <row r="63" ht="409" customHeight="true">
       <c r="A63" s="30" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="64" ht="390" customHeight="true">
+    <row r="64" ht="409" customHeight="true">
       <c r="A64" s="30" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="65" ht="390" customHeight="true">
+    <row r="65" ht="409" customHeight="true">
       <c r="A65" s="30" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="66" ht="390" customHeight="true">
+    <row r="66" ht="409" customHeight="true">
       <c r="A66" s="30" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="67" ht="390" customHeight="true">
+    <row r="67" ht="409" customHeight="true">
       <c r="A67" s="30" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="68" ht="390" customHeight="true">
+    <row r="68" ht="409" customHeight="true">
       <c r="A68" s="30" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="69" ht="390" customHeight="true">
+    <row r="69" ht="409" customHeight="true">
       <c r="A69" s="30" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="70" ht="390" customHeight="true">
+    <row r="70" ht="409" customHeight="true">
       <c r="A70" s="30" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="71" ht="390" customHeight="true">
+    <row r="71" ht="409" customHeight="true">
       <c r="A71" s="30" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="72" ht="390" customHeight="true">
+    <row r="72" ht="409" customHeight="true">
       <c r="A72" s="30" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="73" ht="390" customHeight="true">
+    <row r="73" ht="409" customHeight="true">
       <c r="A73" s="30" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="74" ht="390" customHeight="true">
+    <row r="74" ht="409" customHeight="true">
       <c r="A74" s="30" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="75" ht="390" customHeight="true">
+    <row r="75" ht="409" customHeight="true">
       <c r="A75" s="30" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="76" ht="390" customHeight="true">
+    <row r="76" ht="409" customHeight="true">
       <c r="A76" s="30" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="77" ht="390" customHeight="true">
+    <row r="77" ht="409" customHeight="true">
       <c r="A77" s="30" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="78" ht="390" customHeight="true">
+    <row r="78" ht="409" customHeight="true">
       <c r="A78" s="30" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="79" ht="390" customHeight="true">
+    <row r="79" ht="409" customHeight="true">
       <c r="A79" s="30" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="80" ht="390" customHeight="true">
+    <row r="80" ht="409" customHeight="true">
       <c r="A80" s="30" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="81" ht="390" customHeight="true">
+    <row r="81" ht="409" customHeight="true">
       <c r="A81" s="30" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="82" ht="390" customHeight="true">
+    <row r="82" ht="409" customHeight="true">
       <c r="A82" s="30" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="83" ht="390" customHeight="true">
+    <row r="83" ht="409" customHeight="true">
       <c r="A83" s="30" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="84" ht="390" customHeight="true">
+    <row r="84" ht="409" customHeight="true">
       <c r="A84" s="30" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="85" ht="390" customHeight="true">
+    <row r="85" ht="409" customHeight="true">
       <c r="A85" s="30" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="86" ht="390" customHeight="true">
+    <row r="86" ht="409" customHeight="true">
       <c r="A86" s="30" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="87" ht="390" customHeight="true">
+    <row r="87" ht="409" customHeight="true">
       <c r="A87" s="30" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="88" ht="390" customHeight="true">
+    <row r="88" ht="409" customHeight="true">
       <c r="A88" s="30" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="89" ht="390" customHeight="true">
+    <row r="89" ht="409" customHeight="true">
       <c r="A89" s="30" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="90" ht="390" customHeight="true">
+    <row r="90" ht="409" customHeight="true">
       <c r="A90" s="30" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="91" ht="390" customHeight="true">
+    <row r="91" ht="409" customHeight="true">
       <c r="A91" s="30" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="92" ht="390" customHeight="true">
+    <row r="92" ht="409" customHeight="true">
       <c r="A92" s="30" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="93" ht="390" customHeight="true">
+    <row r="93" ht="409" customHeight="true">
       <c r="A93" s="30" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="94" ht="390" customHeight="true">
+    <row r="94" ht="409" customHeight="true">
       <c r="A94" s="30" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="95" ht="390" customHeight="true">
+    <row r="95" ht="409" customHeight="true">
       <c r="A95" s="30" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="96" ht="390" customHeight="true">
+    <row r="96" ht="409" customHeight="true">
       <c r="A96" s="30" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="97" ht="390" customHeight="true">
+    <row r="97" ht="409" customHeight="true">
       <c r="A97" s="30" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="98" ht="390" customHeight="true">
+    <row r="98" ht="409" customHeight="true">
       <c r="A98" s="30" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="99" ht="390" customHeight="true">
+    <row r="99" ht="409" customHeight="true">
       <c r="A99" s="30" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="100" ht="390" customHeight="true">
+    <row r="100" ht="409" customHeight="true">
       <c r="A100" s="30" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="101" ht="390" customHeight="true">
+    <row r="101" ht="409" customHeight="true">
       <c r="A101" s="30" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="102" ht="390" customHeight="true">
+    <row r="102" ht="409" customHeight="true">
       <c r="A102" s="30" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="103" ht="390" customHeight="true">
+    <row r="103" ht="409" customHeight="true">
       <c r="A103" s="30" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="104" ht="390" customHeight="true">
+    <row r="104" ht="409" customHeight="true">
       <c r="A104" s="30" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="105" ht="390" customHeight="true">
+    <row r="105" ht="409" customHeight="true">
       <c r="A105" s="30" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="106" ht="390" customHeight="true">
+    <row r="106" ht="409" customHeight="true">
       <c r="A106" s="30" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="107" ht="390" customHeight="true">
+    <row r="107" ht="409" customHeight="true">
       <c r="A107" s="30" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="108" ht="390" customHeight="true">
+    <row r="108" ht="409" customHeight="true">
       <c r="A108" s="30" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="109" ht="390" customHeight="true">
+    <row r="109" ht="409" customHeight="true">
       <c r="A109" s="30" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="110" ht="390" customHeight="true">
+    <row r="110" ht="409" customHeight="true">
       <c r="A110" s="30" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="111" ht="390" customHeight="true">
+    <row r="111" ht="409" customHeight="true">
       <c r="A111" s="30" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="112" ht="390" customHeight="true">
+    <row r="112" ht="409" customHeight="true">
       <c r="A112" s="30" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="113" ht="390" customHeight="true">
+    <row r="113" ht="409" customHeight="true">
       <c r="A113" s="30" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="114" ht="390" customHeight="true">
+    <row r="114" ht="409" customHeight="true">
       <c r="A114" s="30" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="115" ht="390" customHeight="true">
+    <row r="115" ht="409" customHeight="true">
       <c r="A115" s="30" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="116" ht="390" customHeight="true">
+    <row r="116" ht="409" customHeight="true">
       <c r="A116" s="30" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="117" ht="390" customHeight="true">
+    <row r="117" ht="409" customHeight="true">
       <c r="A117" s="30" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="118" ht="390" customHeight="true">
+    <row r="118" ht="409" customHeight="true">
       <c r="A118" s="30" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="119" ht="390" customHeight="true">
+    <row r="119" ht="409" customHeight="true">
       <c r="A119" s="30" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="120" ht="390" customHeight="true">
+    <row r="120" ht="409" customHeight="true">
       <c r="A120" s="30" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="121" ht="390" customHeight="true">
+    <row r="121" ht="409" customHeight="true">
       <c r="A121" s="30" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="122" ht="390" customHeight="true">
+    <row r="122" ht="409" customHeight="true">
       <c r="A122" s="30" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="123" ht="390" customHeight="true">
+    <row r="123" ht="409" customHeight="true">
       <c r="A123" s="30" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="124" ht="390" customHeight="true">
+    <row r="124" ht="409" customHeight="true">
       <c r="A124" s="30" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="125" ht="390" customHeight="true">
+    <row r="125" ht="409" customHeight="true">
       <c r="A125" s="30" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="126" ht="390" customHeight="true">
+    <row r="126" ht="409" customHeight="true">
       <c r="A126" s="30" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="127" ht="390" customHeight="true">
+    <row r="127" ht="409" customHeight="true">
       <c r="A127" s="30" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="128" ht="390" customHeight="true">
+    <row r="128" ht="409" customHeight="true">
       <c r="A128" s="30" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="129" ht="390" customHeight="true">
+    <row r="129" ht="409" customHeight="true">
       <c r="A129" s="30" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="130" ht="390" customHeight="true">
+    <row r="130" ht="409" customHeight="true">
       <c r="A130" s="30" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="131" ht="390" customHeight="true">
+    <row r="131" ht="409" customHeight="true">
       <c r="A131" s="30" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="132" ht="390" customHeight="true">
+    <row r="132" ht="409" customHeight="true">
       <c r="A132" s="30" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="133" ht="390" customHeight="true">
+    <row r="133" ht="409" customHeight="true">
       <c r="A133" s="30" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="134" ht="390" customHeight="true">
+    <row r="134" ht="409" customHeight="true">
       <c r="A134" s="30" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="135" ht="390" customHeight="true">
+    <row r="135" ht="409" customHeight="true">
       <c r="A135" s="30" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="136" ht="390" customHeight="true">
+    <row r="136" ht="409" customHeight="true">
       <c r="A136" s="30" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="137" ht="390" customHeight="true">
+    <row r="137" ht="409" customHeight="true">
       <c r="A137" s="30" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="138" ht="390" customHeight="true">
+    <row r="138" ht="409" customHeight="true">
       <c r="A138" s="30" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="139" ht="390" customHeight="true">
+    <row r="139" ht="409" customHeight="true">
       <c r="A139" s="30" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="140" ht="390" customHeight="true">
+    <row r="140" ht="409" customHeight="true">
       <c r="A140" s="30" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="141" ht="390" customHeight="true">
+    <row r="141" ht="409" customHeight="true">
       <c r="A141" s="30" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="142" ht="390" customHeight="true">
+    <row r="142" ht="409" customHeight="true">
       <c r="A142" s="30" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="143" ht="390" customHeight="true">
+    <row r="143" ht="409" customHeight="true">
       <c r="A143" s="30" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="144" ht="390" customHeight="true">
+    <row r="144" ht="409" customHeight="true">
       <c r="A144" s="30" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="145" ht="390" customHeight="true">
+    <row r="145" ht="409" customHeight="true">
       <c r="A145" s="30" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="146" ht="390" customHeight="true">
+    <row r="146" ht="409" customHeight="true">
       <c r="A146" s="30" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="147" ht="390" customHeight="true">
+    <row r="147" ht="409" customHeight="true">
       <c r="A147" s="30" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="148" ht="390" customHeight="true">
+    <row r="148" ht="409" customHeight="true">
       <c r="A148" s="30" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="149" ht="390" customHeight="true">
+    <row r="149" ht="409" customHeight="true">
       <c r="A149" s="30" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="150" ht="390" customHeight="true">
+    <row r="150" ht="409" customHeight="true">
       <c r="A150" s="30" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="151" ht="390" customHeight="true">
+    <row r="151" ht="409" customHeight="true">
       <c r="A151" s="30" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="152" ht="390" customHeight="true">
+    <row r="152" ht="409" customHeight="true">
       <c r="A152" s="30" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="153" ht="390" customHeight="true">
+    <row r="153" ht="409" customHeight="true">
       <c r="A153" s="30" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="154" ht="390" customHeight="true">
+    <row r="154" ht="409" customHeight="true">
       <c r="A154" s="30" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="155" ht="390" customHeight="true">
+    <row r="155" ht="409" customHeight="true">
       <c r="A155" s="30" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="156" ht="390" customHeight="true">
+    <row r="156" ht="409" customHeight="true">
       <c r="A156" s="30" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="157" ht="390" customHeight="true">
+    <row r="157" ht="409" customHeight="true">
       <c r="A157" s="30" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="158" ht="390" customHeight="true">
+    <row r="158" ht="409" customHeight="true">
       <c r="A158" s="30" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="159" ht="390" customHeight="true">
+    <row r="159" ht="409" customHeight="true">
       <c r="A159" s="30" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="160" ht="390" customHeight="true">
+    <row r="160" ht="409" customHeight="true">
       <c r="A160" s="30" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="161" ht="390" customHeight="true">
+    <row r="161" ht="409" customHeight="true">
       <c r="A161" s="30" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="162" ht="390" customHeight="true">
+    <row r="162" ht="409" customHeight="true">
       <c r="A162" s="30" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="163" ht="390" customHeight="true">
+    <row r="163" ht="409" customHeight="true">
       <c r="A163" s="30" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="164" ht="390" customHeight="true">
+    <row r="164" ht="409" customHeight="true">
       <c r="A164" s="30" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="165" ht="390" customHeight="true">
+    <row r="165" ht="409" customHeight="true">
       <c r="A165" s="30" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="166" ht="390" customHeight="true">
+    <row r="166" ht="409" customHeight="true">
       <c r="A166" s="30" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="167" ht="390" customHeight="true">
+    <row r="167" ht="409" customHeight="true">
       <c r="A167" s="30" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="168" ht="390" customHeight="true">
+    <row r="168" ht="409" customHeight="true">
       <c r="A168" s="30" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="169" ht="390" customHeight="true">
+    <row r="169" ht="409" customHeight="true">
       <c r="A169" s="30" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="170" ht="390" customHeight="true">
+    <row r="170" ht="409" customHeight="true">
       <c r="A170" s="30" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="171" ht="390" customHeight="true">
+    <row r="171" ht="409" customHeight="true">
       <c r="A171" s="30" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="172" ht="390" customHeight="true">
+    <row r="172" ht="409" customHeight="true">
       <c r="A172" s="30" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="173" ht="390" customHeight="true">
+    <row r="173" ht="409" customHeight="true">
       <c r="A173" s="30" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="174" ht="390" customHeight="true">
+    <row r="174" ht="409" customHeight="true">
       <c r="A174" s="30" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="175" ht="390" customHeight="true">
+    <row r="175" ht="409" customHeight="true">
       <c r="A175" s="30" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="176" ht="390" customHeight="true">
+    <row r="176" ht="409" customHeight="true">
       <c r="A176" s="30" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="177" ht="390" customHeight="true">
+    <row r="177" ht="409" customHeight="true">
       <c r="A177" s="30" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="178" ht="390" customHeight="true">
+    <row r="178" ht="409" customHeight="true">
       <c r="A178" s="30" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="179" ht="390" customHeight="true">
+    <row r="179" ht="409" customHeight="true">
       <c r="A179" s="30" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="180" ht="390" customHeight="true">
+    <row r="180" ht="409" customHeight="true">
       <c r="A180" s="30" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="181" ht="390" customHeight="true">
+    <row r="181" ht="409" customHeight="true">
       <c r="A181" s="30" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="182" ht="390" customHeight="true">
+    <row r="182" ht="409" customHeight="true">
       <c r="A182" s="30" t="s">
         <v>343</v>
       </c>

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -1361,7 +1361,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="200"/>
+      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -4718,7 +4718,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="90"/>
+    <col customWidth="true" max="1" min="1" width="110"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -23,6 +23,10 @@
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$66</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$P$259</definedName>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$K$44</definedName>
+    <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 2'!$A$1:$K$38</definedName>
+    <definedName localSheetId="7" name="_xlnm.Print_Area">'Tree 3'!$A$1:$K$43</definedName>
+    <definedName localSheetId="8" name="_xlnm.Print_Area">'Tree 4'!$A$1:$K$38</definedName>
     <definedName localSheetId="9" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$46</definedName>
     <definedName localSheetId="10" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$45</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$271</definedName>
@@ -3172,12 +3176,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3194,11 +3203,6 @@
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -3550,20 +3554,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3580,11 +3589,6 @@
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -3913,10 +3917,10 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -14642,12 +14646,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14664,11 +14673,6 @@
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -15025,20 +15029,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15055,11 +15064,6 @@
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -15388,9 +15392,9 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -1559,7 +1559,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
@@ -3218,6 +3218,8 @@
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$50</f>
       </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="23" t="str">
         <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
       </c>
@@ -3604,6 +3606,8 @@
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$74</f>
       </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="23" t="str">
         <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O16)</f>
       </c>
@@ -14688,6 +14692,8 @@
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$4</f>
       </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="23" t="str">
         <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G17)</f>
       </c>
@@ -15079,6 +15085,8 @@
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$29</f>
       </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="23" t="str">
         <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O35)</f>
       </c>

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -3213,21 +3213,28 @@
       <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$49</f>
       </c>
+      <c r="C5" s="23" t="str">
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O16)</f>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$50</f>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
+      <c r="D6" s="22"/>
+      <c r="E6" s="21">
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$51</f>
       </c>
+      <c r="C7" s="23" t="str">
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G18)</f>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
     </row>
@@ -3242,7 +3249,7 @@
         <f>'data'!$A$54</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G18)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O35)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3254,7 +3261,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -3265,7 +3272,7 @@
         <f>"2. " &amp; data!$B$53</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3282,7 +3289,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O52)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3294,7 +3301,7 @@
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -3304,7 +3311,7 @@
         <f>"1. " &amp; data!$B$55</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G87)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3329,7 +3336,7 @@
         <f>"3. " &amp; data!$B$57</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G103)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O69)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3338,7 +3345,7 @@
       <c r="A18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -3349,7 +3356,7 @@
         <f>'data'!$A$60</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G121)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3368,7 +3375,7 @@
         <f>"2. " &amp; data!$B$59</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G137)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O86)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3378,14 +3385,14 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K22" s="20"/>
     </row>
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G155)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G87)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3407,7 +3414,7 @@
         <f>"1. " &amp; data!$B$61</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G171)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O103)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3420,7 +3427,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -3432,7 +3439,7 @@
         <f>"3. " &amp; data!$B$63</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G189)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G104)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3452,7 +3459,7 @@
         <f>'data'!$A$66</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G205)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O120)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -3462,7 +3469,7 @@
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -3471,7 +3478,7 @@
         <f>"2. " &amp; data!$B$65</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G223)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G121)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3492,7 +3499,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G239)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O137)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -3502,7 +3509,7 @@
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="20"/>
@@ -3512,7 +3519,7 @@
         <f>"1. " &amp; data!$B$67</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G138)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -3601,21 +3608,28 @@
       <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$73</f>
       </c>
+      <c r="C5" s="23" t="str">
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O154)</f>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$74</f>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O16)</f>
+      <c r="D6" s="22"/>
+      <c r="E6" s="21">
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$75</f>
       </c>
+      <c r="C7" s="23" t="str">
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G155)</f>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
     </row>
@@ -3630,7 +3644,7 @@
         <f>'data'!$A$78</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O52)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O171)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3642,7 +3656,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -3653,7 +3667,7 @@
         <f>"2. " &amp; data!$B$77</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O36)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G172)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3670,7 +3684,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O86)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O188)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3682,7 +3696,7 @@
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -3692,7 +3706,7 @@
         <f>"1. " &amp; data!$B$79</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O70)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G189)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3717,7 +3731,7 @@
         <f>"3. " &amp; data!$B$81</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O120)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O205)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3726,7 +3740,7 @@
       <c r="A18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -3737,7 +3751,7 @@
         <f>'data'!$A$84</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O104)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G206)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3756,7 +3770,7 @@
         <f>"2. " &amp; data!$B$83</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O154)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O222)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3766,14 +3780,14 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K22" s="20"/>
     </row>
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O138)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G223)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3795,7 +3809,7 @@
         <f>"1. " &amp; data!$B$85</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O188)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O239)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3808,7 +3822,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -3820,7 +3834,7 @@
         <f>"3. " &amp; data!$B$87</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O172)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G240)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3839,18 +3853,16 @@
       <c r="A29" s="24" t="str">
         <f>'data'!$A$90</f>
       </c>
-      <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O222)</f>
-      </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30">
       <c r="A30" s="25" t="str">
         <f>"1. " &amp; data!$B$88</f>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="21">
-        <v>27</v>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23" t="str">
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -3858,11 +3870,6 @@
       <c r="A31" s="26" t="str">
         <f>"2. " &amp; data!$B$89</f>
       </c>
-      <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O206)</f>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="20"/>
       <c r="F31" s="22"/>
       <c r="G31" s="20"/>
       <c r="I31" s="20"/>
@@ -3879,18 +3886,16 @@
     </row>
     <row r="33">
       <c r="A33" s="22"/>
-      <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
-      </c>
       <c r="G33" s="20"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="str">
         <f>'data'!$A$93</f>
       </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="21">
-        <v>28</v>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23" t="str">
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="20"/>
@@ -3899,11 +3904,6 @@
       <c r="A35" s="25" t="str">
         <f>"1. " &amp; data!$B$91</f>
       </c>
-      <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O240)</f>
-      </c>
-      <c r="D35" s="15"/>
-      <c r="E35" s="20"/>
     </row>
     <row r="36">
       <c r="A36" s="26" t="str">
@@ -12127,7 +12127,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O17)</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -12135,10 +12135,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G17)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G18)</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -12146,7 +12146,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G18)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O16)</f>
       </c>
     </row>
     <row r="6">
@@ -12211,7 +12211,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O36)</f>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -12219,10 +12219,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G86)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G87)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -12230,7 +12230,7 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O35)</f>
       </c>
     </row>
     <row r="14">
@@ -12295,7 +12295,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G104)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O53)</f>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -12303,10 +12303,10 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G120)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G121)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
       </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -12314,7 +12314,7 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G103)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O52)</f>
       </c>
     </row>
     <row r="22">
@@ -12379,7 +12379,7 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G138)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O70)</f>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -12387,10 +12387,10 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G154)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G155)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -12398,7 +12398,7 @@
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G137)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O69)</f>
       </c>
     </row>
     <row r="30">
@@ -12463,7 +12463,7 @@
     </row>
     <row r="36">
       <c r="A36" s="14" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G172)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O87)</f>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -12471,10 +12471,10 @@
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
       <c r="G36" s="14" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G188)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G86)</f>
       </c>
       <c r="I36" s="14" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G189)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G87)</f>
       </c>
       <c r="J36" s="18"/>
       <c r="K36" s="18"/>
@@ -12482,7 +12482,7 @@
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
       <c r="O36" s="14" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G171)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O86)</f>
       </c>
     </row>
     <row r="38">
@@ -12547,7 +12547,7 @@
     </row>
     <row r="44">
       <c r="A44" s="14" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G206)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O104)</f>
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
@@ -12555,10 +12555,10 @@
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="14" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G222)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G103)</f>
       </c>
       <c r="I44" s="14" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G223)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G104)</f>
       </c>
       <c r="J44" s="18"/>
       <c r="K44" s="18"/>
@@ -12566,7 +12566,7 @@
       <c r="M44" s="18"/>
       <c r="N44" s="18"/>
       <c r="O44" s="14" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G205)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O103)</f>
       </c>
     </row>
     <row r="46">
@@ -12631,7 +12631,7 @@
     </row>
     <row r="52">
       <c r="A52" s="14" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G240)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O121)</f>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -12639,10 +12639,10 @@
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G120)</f>
       </c>
       <c r="I52" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G121)</f>
       </c>
       <c r="J52" s="18"/>
       <c r="K52" s="18"/>
@@ -12650,7 +12650,7 @@
       <c r="M52" s="18"/>
       <c r="N52" s="18"/>
       <c r="O52" s="14" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G239)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O120)</f>
       </c>
     </row>
     <row r="54">
@@ -12715,7 +12715,7 @@
     </row>
     <row r="60">
       <c r="A60" s="14" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O53)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O138)</f>
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
@@ -12723,10 +12723,10 @@
       <c r="E60" s="18"/>
       <c r="F60" s="18"/>
       <c r="G60" s="14" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O17)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G137)</f>
       </c>
       <c r="I60" s="14" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O36)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G138)</f>
       </c>
       <c r="J60" s="18"/>
       <c r="K60" s="18"/>
@@ -12734,7 +12734,7 @@
       <c r="M60" s="18"/>
       <c r="N60" s="18"/>
       <c r="O60" s="14" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O52)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O137)</f>
       </c>
     </row>
     <row r="62">
@@ -12799,7 +12799,7 @@
     </row>
     <row r="68">
       <c r="A68" s="14" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O87)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O155)</f>
       </c>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -12807,10 +12807,10 @@
       <c r="E68" s="18"/>
       <c r="F68" s="18"/>
       <c r="G68" s="14" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O69)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G154)</f>
       </c>
       <c r="I68" s="14" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O70)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G155)</f>
       </c>
       <c r="J68" s="18"/>
       <c r="K68" s="18"/>
@@ -12818,7 +12818,7 @@
       <c r="M68" s="18"/>
       <c r="N68" s="18"/>
       <c r="O68" s="14" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O86)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O154)</f>
       </c>
     </row>
     <row r="70">
@@ -12883,7 +12883,7 @@
     </row>
     <row r="76">
       <c r="A76" s="14" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O121)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O172)</f>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -12891,10 +12891,10 @@
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
       <c r="G76" s="14" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O103)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G171)</f>
       </c>
       <c r="I76" s="14" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O104)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G172)</f>
       </c>
       <c r="J76" s="18"/>
       <c r="K76" s="18"/>
@@ -12902,7 +12902,7 @@
       <c r="M76" s="18"/>
       <c r="N76" s="18"/>
       <c r="O76" s="14" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O120)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O171)</f>
       </c>
     </row>
     <row r="78">
@@ -12967,7 +12967,7 @@
     </row>
     <row r="84">
       <c r="A84" s="14" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O155)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O189)</f>
       </c>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
@@ -12975,10 +12975,10 @@
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
       <c r="G84" s="14" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O137)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G188)</f>
       </c>
       <c r="I84" s="14" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O138)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G189)</f>
       </c>
       <c r="J84" s="18"/>
       <c r="K84" s="18"/>
@@ -12986,7 +12986,7 @@
       <c r="M84" s="18"/>
       <c r="N84" s="18"/>
       <c r="O84" s="14" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O154)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O188)</f>
       </c>
     </row>
     <row r="86">
@@ -13051,7 +13051,7 @@
     </row>
     <row r="92">
       <c r="A92" s="14" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O189)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O206)</f>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
@@ -13059,10 +13059,10 @@
       <c r="E92" s="18"/>
       <c r="F92" s="18"/>
       <c r="G92" s="14" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O171)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G205)</f>
       </c>
       <c r="I92" s="14" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O172)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G206)</f>
       </c>
       <c r="J92" s="18"/>
       <c r="K92" s="18"/>
@@ -13070,7 +13070,7 @@
       <c r="M92" s="18"/>
       <c r="N92" s="18"/>
       <c r="O92" s="14" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O188)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O205)</f>
       </c>
     </row>
     <row r="94">
@@ -13143,10 +13143,10 @@
       <c r="E100" s="18"/>
       <c r="F100" s="18"/>
       <c r="G100" s="14" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O205)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G222)</f>
       </c>
       <c r="I100" s="14" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O206)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G223)</f>
       </c>
       <c r="J100" s="18"/>
       <c r="K100" s="18"/>
@@ -13219,7 +13219,7 @@
     </row>
     <row r="108">
       <c r="A108" s="14" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O240)</f>
       </c>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -13227,10 +13227,10 @@
       <c r="E108" s="18"/>
       <c r="F108" s="18"/>
       <c r="G108" s="14" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O239)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G239)</f>
       </c>
       <c r="I108" s="14" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O240)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G240)</f>
       </c>
       <c r="J108" s="18"/>
       <c r="K108" s="18"/>
@@ -13238,7 +13238,7 @@
       <c r="M108" s="18"/>
       <c r="N108" s="18"/>
       <c r="O108" s="14" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O239)</f>
       </c>
     </row>
     <row r="110">
@@ -13303,7 +13303,7 @@
     </row>
     <row r="121">
       <c r="A121" s="14" t="str">
-        <f>CONCATENATE("M 1 ",G6)</f>
+        <f>CONCATENATE("M 2 ",G14)</f>
       </c>
       <c r="B121" s="18"/>
       <c r="C121" s="18"/>
@@ -13311,10 +13311,10 @@
       <c r="E121" s="18"/>
       <c r="F121" s="18"/>
       <c r="G121" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G17)</f>
+        <f>CONCATENATE("M 1 ",G6)</f>
       </c>
       <c r="I121" s="14" t="str">
-        <f>CONCATENATE("M 15 ",O6)</f>
+        <f>CONCATENATE("M 16 ",O14)</f>
       </c>
       <c r="J121" s="18"/>
       <c r="K121" s="18"/>
@@ -13322,7 +13322,7 @@
       <c r="M121" s="18"/>
       <c r="N121" s="18"/>
       <c r="O121" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
+        <f>CONCATENATE("M 15 ",O6)</f>
       </c>
     </row>
     <row r="123">
@@ -13387,7 +13387,7 @@
     </row>
     <row r="129">
       <c r="A129" s="14" t="str">
-        <f>CONCATENATE("M 3 ",G22)</f>
+        <f>CONCATENATE("M 4 ",G30)</f>
       </c>
       <c r="B129" s="18"/>
       <c r="C129" s="18"/>
@@ -13395,10 +13395,10 @@
       <c r="E129" s="18"/>
       <c r="F129" s="18"/>
       <c r="G129" s="14" t="str">
-        <f>CONCATENATE("M 2 ",G14)</f>
+        <f>CONCATENATE("M 3 ",G22)</f>
       </c>
       <c r="I129" s="14" t="str">
-        <f>CONCATENATE("M 17 ",O22)</f>
+        <f>CONCATENATE("M 18 ",O30)</f>
       </c>
       <c r="J129" s="18"/>
       <c r="K129" s="18"/>
@@ -13406,7 +13406,7 @@
       <c r="M129" s="18"/>
       <c r="N129" s="18"/>
       <c r="O129" s="14" t="str">
-        <f>CONCATENATE("M 16 ",O14)</f>
+        <f>CONCATENATE("M 17 ",O22)</f>
       </c>
     </row>
     <row r="131">
@@ -13471,7 +13471,7 @@
     </row>
     <row r="137">
       <c r="A137" s="14" t="str">
-        <f>CONCATENATE("M 5 ",G38)</f>
+        <f>CONCATENATE("M 6 ",G46)</f>
       </c>
       <c r="B137" s="18"/>
       <c r="C137" s="18"/>
@@ -13479,10 +13479,10 @@
       <c r="E137" s="18"/>
       <c r="F137" s="18"/>
       <c r="G137" s="14" t="str">
-        <f>CONCATENATE("M 4 ",G30)</f>
+        <f>CONCATENATE("M 5 ",G38)</f>
       </c>
       <c r="I137" s="14" t="str">
-        <f>CONCATENATE("M 19 ",O38)</f>
+        <f>CONCATENATE("M 20 ",O46)</f>
       </c>
       <c r="J137" s="18"/>
       <c r="K137" s="18"/>
@@ -13490,7 +13490,7 @@
       <c r="M137" s="18"/>
       <c r="N137" s="18"/>
       <c r="O137" s="14" t="str">
-        <f>CONCATENATE("M 18 ",O30)</f>
+        <f>CONCATENATE("M 19 ",O38)</f>
       </c>
     </row>
     <row r="139">
@@ -13555,7 +13555,7 @@
     </row>
     <row r="145">
       <c r="A145" s="14" t="str">
-        <f>CONCATENATE("M 7 ",G54)</f>
+        <f>CONCATENATE("M 8 ",G62)</f>
       </c>
       <c r="B145" s="18"/>
       <c r="C145" s="18"/>
@@ -13563,10 +13563,10 @@
       <c r="E145" s="18"/>
       <c r="F145" s="18"/>
       <c r="G145" s="14" t="str">
-        <f>CONCATENATE("M 6 ",G46)</f>
+        <f>CONCATENATE("M 7 ",G54)</f>
       </c>
       <c r="I145" s="14" t="str">
-        <f>CONCATENATE("M 21 ",O54)</f>
+        <f>CONCATENATE("M 22 ",O62)</f>
       </c>
       <c r="J145" s="18"/>
       <c r="K145" s="18"/>
@@ -13574,7 +13574,7 @@
       <c r="M145" s="18"/>
       <c r="N145" s="18"/>
       <c r="O145" s="14" t="str">
-        <f>CONCATENATE("M 20 ",O46)</f>
+        <f>CONCATENATE("M 21 ",O54)</f>
       </c>
     </row>
     <row r="147">
@@ -13639,7 +13639,7 @@
     </row>
     <row r="153">
       <c r="A153" s="14" t="str">
-        <f>CONCATENATE("M 8 ",G62)</f>
+        <f>CONCATENATE("M 10 ",G78)</f>
       </c>
       <c r="B153" s="18"/>
       <c r="C153" s="18"/>
@@ -13647,10 +13647,10 @@
       <c r="E153" s="18"/>
       <c r="F153" s="18"/>
       <c r="G153" s="14" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O35)</f>
+        <f>CONCATENATE("M 9 ",G70)</f>
       </c>
       <c r="I153" s="14" t="str">
-        <f>CONCATENATE("M 22 ",O62)</f>
+        <f>CONCATENATE("M 24 ",O78)</f>
       </c>
       <c r="J153" s="18"/>
       <c r="K153" s="18"/>
@@ -13658,7 +13658,7 @@
       <c r="M153" s="18"/>
       <c r="N153" s="18"/>
       <c r="O153" s="14" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!O16)</f>
+        <f>CONCATENATE("M 23 ",O70)</f>
       </c>
     </row>
     <row r="155">
@@ -13723,7 +13723,7 @@
     </row>
     <row r="161">
       <c r="A161" s="14" t="str">
-        <f>CONCATENATE("M 10 ",G78)</f>
+        <f>CONCATENATE("M 12 ",G94)</f>
       </c>
       <c r="B161" s="18"/>
       <c r="C161" s="18"/>
@@ -13731,10 +13731,10 @@
       <c r="E161" s="18"/>
       <c r="F161" s="18"/>
       <c r="G161" s="14" t="str">
-        <f>CONCATENATE("M 9 ",G70)</f>
+        <f>CONCATENATE("M 11 ",G86)</f>
       </c>
       <c r="I161" s="14" t="str">
-        <f>CONCATENATE("M 24 ",O78)</f>
+        <f>CONCATENATE("M 26 ",O94)</f>
       </c>
       <c r="J161" s="18"/>
       <c r="K161" s="18"/>
@@ -13742,7 +13742,7 @@
       <c r="M161" s="18"/>
       <c r="N161" s="18"/>
       <c r="O161" s="14" t="str">
-        <f>CONCATENATE("M 23 ",O70)</f>
+        <f>CONCATENATE("M 25 ",O86)</f>
       </c>
     </row>
     <row r="163">
@@ -13807,7 +13807,7 @@
     </row>
     <row r="169">
       <c r="A169" s="14" t="str">
-        <f>CONCATENATE("M 12 ",G94)</f>
+        <f>CONCATENATE("M 14 ",G110)</f>
       </c>
       <c r="B169" s="18"/>
       <c r="C169" s="18"/>
@@ -13815,10 +13815,10 @@
       <c r="E169" s="18"/>
       <c r="F169" s="18"/>
       <c r="G169" s="14" t="str">
-        <f>CONCATENATE("M 11 ",G86)</f>
+        <f>CONCATENATE("M 13 ",G102)</f>
       </c>
       <c r="I169" s="14" t="str">
-        <f>CONCATENATE("M 26 ",O94)</f>
+        <f>CONCATENATE("M 28 ",O110)</f>
       </c>
       <c r="J169" s="18"/>
       <c r="K169" s="18"/>
@@ -13826,7 +13826,7 @@
       <c r="M169" s="18"/>
       <c r="N169" s="18"/>
       <c r="O169" s="14" t="str">
-        <f>CONCATENATE("M 25 ",O86)</f>
+        <f>CONCATENATE("M 27 ",O102)</f>
       </c>
     </row>
     <row r="171">
@@ -13891,7 +13891,7 @@
     </row>
     <row r="177">
       <c r="A177" s="14" t="str">
-        <f>CONCATENATE("M 14 ",G110)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
       </c>
       <c r="B177" s="18"/>
       <c r="C177" s="18"/>
@@ -13899,10 +13899,10 @@
       <c r="E177" s="18"/>
       <c r="F177" s="18"/>
       <c r="G177" s="14" t="str">
-        <f>CONCATENATE("M 13 ",G102)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
       </c>
       <c r="I177" s="14" t="str">
-        <f>CONCATENATE("M 28 ",O110)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
       </c>
       <c r="J177" s="18"/>
       <c r="K177" s="18"/>
@@ -13910,7 +13910,7 @@
       <c r="M177" s="18"/>
       <c r="N177" s="18"/>
       <c r="O177" s="14" t="str">
-        <f>CONCATENATE("M 27 ",O102)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
       </c>
     </row>
     <row r="179">
@@ -14687,21 +14687,28 @@
       <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$3</f>
       </c>
+      <c r="C5" s="23" t="str">
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G17)</f>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$4</f>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G17)</f>
+      <c r="D6" s="22"/>
+      <c r="E6" s="21">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="str">
         <f>"3. " &amp; data!$B$5</f>
       </c>
+      <c r="C7" s="23" t="str">
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O17)</f>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
     </row>
@@ -14716,7 +14723,7 @@
     <row r="9">
       <c r="A9" s="22"/>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -14728,7 +14735,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -14739,7 +14746,7 @@
         <f>"1. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O36)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -14758,7 +14765,7 @@
         <f>"3. " &amp; data!$B$9</f>
       </c>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G86)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -14768,7 +14775,7 @@
       <c r="A14" s="22"/>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -14778,7 +14785,7 @@
         <f>'data'!$A$12</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O53)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -14803,7 +14810,7 @@
         <f>"2. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G120)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -14814,7 +14821,7 @@
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -14823,7 +14830,7 @@
     <row r="19">
       <c r="A19" s="22"/>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G104)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O70)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -14842,7 +14849,7 @@
         <f>"1. " &amp; data!$B$13</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G154)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G86)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -14852,7 +14859,7 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="20"/>
     </row>
@@ -14861,7 +14868,7 @@
         <f>"3. " &amp; data!$B$15</f>
       </c>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G138)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O87)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -14881,7 +14888,7 @@
         <f>'data'!$A$18</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G188)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G103)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -14894,7 +14901,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -14906,7 +14913,7 @@
         <f>"2. " &amp; data!$B$17</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G172)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O104)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -14926,7 +14933,7 @@
     <row r="29">
       <c r="A29" s="22"/>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G222)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G120)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -14936,7 +14943,7 @@
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -14945,7 +14952,7 @@
         <f>"1. " &amp; data!$B$19</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G206)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O121)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -14968,7 +14975,7 @@
         <f>"3. " &amp; data!$B$21</f>
       </c>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G137)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -14976,7 +14983,7 @@
       <c r="A34" s="22"/>
       <c r="D34" s="22"/>
       <c r="E34" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="20"/>
@@ -14986,7 +14993,7 @@
         <f>'data'!$A$24</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G240)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O138)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -15080,21 +15087,28 @@
       <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$28</f>
       </c>
+      <c r="C5" s="23" t="str">
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G154)</f>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$29</f>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O35)</f>
+      <c r="D6" s="22"/>
+      <c r="E6" s="21">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$30</f>
       </c>
+      <c r="C7" s="23" t="str">
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O155)</f>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
     </row>
@@ -15109,7 +15123,7 @@
         <f>'data'!$A$33</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!O17)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G171)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -15121,7 +15135,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -15132,7 +15146,7 @@
         <f>"2. " &amp; data!$B$32</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O53)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O172)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -15149,7 +15163,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O69)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G188)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -15161,7 +15175,7 @@
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -15171,7 +15185,7 @@
         <f>"1. " &amp; data!$B$34</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O87)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O189)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -15196,7 +15210,7 @@
         <f>"3. " &amp; data!$B$36</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O103)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G205)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -15205,7 +15219,7 @@
       <c r="A18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -15216,7 +15230,7 @@
         <f>'data'!$A$39</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O121)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O206)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -15235,7 +15249,7 @@
         <f>"2. " &amp; data!$B$38</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O137)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G222)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -15245,14 +15259,14 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K22" s="20"/>
     </row>
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O155)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O223)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -15274,7 +15288,7 @@
         <f>"1. " &amp; data!$B$40</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O171)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G239)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -15287,7 +15301,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -15299,7 +15313,7 @@
         <f>"3. " &amp; data!$B$42</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O189)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O240)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -15318,18 +15332,16 @@
       <c r="A29" s="24" t="str">
         <f>'data'!$A$45</f>
       </c>
-      <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O205)</f>
-      </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30">
       <c r="A30" s="25" t="str">
         <f>"1. " &amp; data!$B$43</f>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="21">
-        <v>13</v>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23" t="str">
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -15337,11 +15349,6 @@
       <c r="A31" s="26" t="str">
         <f>"2. " &amp; data!$B$44</f>
       </c>
-      <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O223)</f>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="20"/>
       <c r="F31" s="22"/>
       <c r="G31" s="20"/>
       <c r="I31" s="20"/>
@@ -15358,18 +15365,16 @@
     </row>
     <row r="33">
       <c r="A33" s="22"/>
-      <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O239)</f>
-      </c>
       <c r="G33" s="20"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="str">
         <f>'data'!$A$48</f>
       </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="21">
-        <v>14</v>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23" t="str">
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="20"/>
@@ -15378,11 +15383,6 @@
       <c r="A35" s="25" t="str">
         <f>"1. " &amp; data!$B$46</f>
       </c>
-      <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
-      </c>
-      <c r="D35" s="15"/>
-      <c r="E35" s="20"/>
     </row>
     <row r="36">
       <c r="A36" s="26" t="str">

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -1073,130 +1073,130 @@
     <t>Round 1 - Match 1</t>
   </si>
   <si>
+    <t>Round 1 - Match 16</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 2</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 17</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 3</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 18</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 4</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 19</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 5</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 20</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 6</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 21</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 7</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 22</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 8</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 23</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 9</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 24</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 10</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 25</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 11</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 26</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 12</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 27</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 13</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 28</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 14</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 29</t>
+  </si>
+  <si>
     <t>Round 1 - Match 15</t>
   </si>
   <si>
-    <t>Round 1 - Match 2</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 16</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 3</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 17</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 4</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 18</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 5</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 19</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 6</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 20</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 7</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 21</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 8</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 22</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 9</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 23</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 10</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 24</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 11</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 25</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 12</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 26</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 13</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 27</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 14</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 28</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 29</t>
+    <t>Round 1 - Match 30</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 31</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 38</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 32</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 39</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 33</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 40</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 34</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 41</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 35</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 42</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 36</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 43</t>
   </si>
   <si>
     <t>Round 2 - Match 37</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 30</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 38</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 31</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 39</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 32</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 40</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 33</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 41</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 34</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 42</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 35</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 43</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 36</t>
   </si>
   <si>
     <t>Round 2 - Match 44</t>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -3241,7 +3241,7 @@
     <row r="8">
       <c r="A8" s="22"/>
       <c r="G8" s="21">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -3325,7 +3325,7 @@
         <f>"2. " &amp; data!$B$56</f>
       </c>
       <c r="G16" s="21">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -3345,7 +3345,7 @@
       <c r="A18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K22" s="20"/>
     </row>
@@ -3405,7 +3405,7 @@
         <f>'data'!$A$63</f>
       </c>
       <c r="G24" s="21">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -3491,7 +3491,7 @@
         <f>"3. " &amp; data!$B$66</f>
       </c>
       <c r="G32" s="21">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="20"/>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -3636,7 +3636,7 @@
     <row r="8">
       <c r="A8" s="22"/>
       <c r="G8" s="21">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -3720,7 +3720,7 @@
         <f>"2. " &amp; data!$B$80</f>
       </c>
       <c r="G16" s="21">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -3740,7 +3740,7 @@
       <c r="A18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K22" s="20"/>
     </row>
@@ -3800,7 +3800,7 @@
         <f>'data'!$A$87</f>
       </c>
       <c r="G24" s="21">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -3853,16 +3853,18 @@
       <c r="A29" s="24" t="str">
         <f>'data'!$A$90</f>
       </c>
+      <c r="C29" s="23" t="str">
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
+      </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30">
       <c r="A30" s="25" t="str">
         <f>"1. " &amp; data!$B$88</f>
       </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
+      <c r="D30" s="22"/>
+      <c r="E30" s="21">
+        <v>30</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -3870,35 +3872,27 @@
       <c r="A31" s="26" t="str">
         <f>"2. " &amp; data!$B$89</f>
       </c>
-      <c r="F31" s="22"/>
-      <c r="G31" s="20"/>
+      <c r="C31" s="23" t="str">
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="20"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32">
       <c r="A32" s="27" t="str">
         <f>"3. " &amp; data!$B$90</f>
       </c>
-      <c r="G32" s="21">
-        <v>44</v>
-      </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
     </row>
     <row r="33">
       <c r="A33" s="22"/>
-      <c r="G33" s="20"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="str">
         <f>'data'!$A$93</f>
       </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
-      </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="20"/>
     </row>
     <row r="35">
       <c r="A35" s="25" t="str">
@@ -13261,89 +13255,89 @@
       </c>
       <c r="O111" s="19"/>
     </row>
+    <row r="114">
+      <c r="A114" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="B114" s="13"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="13"/>
+      <c r="E114" s="13"/>
+      <c r="F114" s="13"/>
+      <c r="G114" s="13"/>
+      <c r="I114" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="J114" s="13"/>
+      <c r="K114" s="13"/>
+      <c r="L114" s="13"/>
+      <c r="M114" s="13"/>
+      <c r="N114" s="13"/>
+      <c r="O114" s="13"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D115" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="G115" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="I115" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="L115" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="O115" s="16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="str">
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
+      </c>
+      <c r="B116" s="18"/>
+      <c r="C116" s="18"/>
+      <c r="D116" s="18"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="18"/>
+      <c r="G116" s="14" t="str">
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
+      </c>
+      <c r="I116" s="14" t="str">
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
+      </c>
+      <c r="J116" s="18"/>
+      <c r="K116" s="18"/>
+      <c r="L116" s="18"/>
+      <c r="M116" s="18"/>
+      <c r="N116" s="18"/>
+      <c r="O116" s="14" t="str">
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
+      </c>
+    </row>
+    <row r="118">
+      <c r="F118" t="s">
+        <v>249</v>
+      </c>
+      <c r="G118" s="19"/>
+      <c r="N118" t="s">
+        <v>249</v>
+      </c>
+      <c r="O118" s="19"/>
+    </row>
     <row r="119">
-      <c r="A119" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="B119" s="13"/>
-      <c r="C119" s="13"/>
-      <c r="D119" s="13"/>
-      <c r="E119" s="13"/>
-      <c r="F119" s="13"/>
-      <c r="G119" s="13"/>
-      <c r="I119" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="J119" s="13"/>
-      <c r="K119" s="13"/>
-      <c r="L119" s="13"/>
-      <c r="M119" s="13"/>
-      <c r="N119" s="13"/>
-      <c r="O119" s="13"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="D120" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="G120" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="I120" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="L120" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="O120" s="16" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="14" t="str">
-        <f>CONCATENATE("M 2 ",G14)</f>
-      </c>
-      <c r="B121" s="18"/>
-      <c r="C121" s="18"/>
-      <c r="D121" s="18"/>
-      <c r="E121" s="18"/>
-      <c r="F121" s="18"/>
-      <c r="G121" s="14" t="str">
-        <f>CONCATENATE("M 1 ",G6)</f>
-      </c>
-      <c r="I121" s="14" t="str">
-        <f>CONCATENATE("M 16 ",O14)</f>
-      </c>
-      <c r="J121" s="18"/>
-      <c r="K121" s="18"/>
-      <c r="L121" s="18"/>
-      <c r="M121" s="18"/>
-      <c r="N121" s="18"/>
-      <c r="O121" s="14" t="str">
-        <f>CONCATENATE("M 15 ",O6)</f>
-      </c>
-    </row>
-    <row r="123">
-      <c r="F123" t="s">
-        <v>249</v>
-      </c>
-      <c r="G123" s="19"/>
-      <c r="N123" t="s">
-        <v>249</v>
-      </c>
-      <c r="O123" s="19"/>
-    </row>
-    <row r="124">
-      <c r="F124" t="s">
+      <c r="F119" t="s">
         <v>250</v>
       </c>
-      <c r="G124" s="19"/>
-      <c r="N124" t="s">
+      <c r="G119" s="19"/>
+      <c r="N119" t="s">
         <v>250</v>
       </c>
-      <c r="O124" s="19"/>
+      <c r="O119" s="19"/>
     </row>
     <row r="127">
       <c r="A127" s="13" t="s">
@@ -13387,7 +13381,7 @@
     </row>
     <row r="129">
       <c r="A129" s="14" t="str">
-        <f>CONCATENATE("M 4 ",G30)</f>
+        <f>CONCATENATE("M 2 ",G14)</f>
       </c>
       <c r="B129" s="18"/>
       <c r="C129" s="18"/>
@@ -13395,10 +13389,10 @@
       <c r="E129" s="18"/>
       <c r="F129" s="18"/>
       <c r="G129" s="14" t="str">
-        <f>CONCATENATE("M 3 ",G22)</f>
+        <f>CONCATENATE("M 1 ",G6)</f>
       </c>
       <c r="I129" s="14" t="str">
-        <f>CONCATENATE("M 18 ",O30)</f>
+        <f>CONCATENATE("M 17 ",O14)</f>
       </c>
       <c r="J129" s="18"/>
       <c r="K129" s="18"/>
@@ -13406,7 +13400,7 @@
       <c r="M129" s="18"/>
       <c r="N129" s="18"/>
       <c r="O129" s="14" t="str">
-        <f>CONCATENATE("M 17 ",O22)</f>
+        <f>CONCATENATE("M 16 ",O6)</f>
       </c>
     </row>
     <row r="131">
@@ -13471,7 +13465,7 @@
     </row>
     <row r="137">
       <c r="A137" s="14" t="str">
-        <f>CONCATENATE("M 6 ",G46)</f>
+        <f>CONCATENATE("M 4 ",G30)</f>
       </c>
       <c r="B137" s="18"/>
       <c r="C137" s="18"/>
@@ -13479,10 +13473,10 @@
       <c r="E137" s="18"/>
       <c r="F137" s="18"/>
       <c r="G137" s="14" t="str">
-        <f>CONCATENATE("M 5 ",G38)</f>
+        <f>CONCATENATE("M 3 ",G22)</f>
       </c>
       <c r="I137" s="14" t="str">
-        <f>CONCATENATE("M 20 ",O46)</f>
+        <f>CONCATENATE("M 19 ",O30)</f>
       </c>
       <c r="J137" s="18"/>
       <c r="K137" s="18"/>
@@ -13490,7 +13484,7 @@
       <c r="M137" s="18"/>
       <c r="N137" s="18"/>
       <c r="O137" s="14" t="str">
-        <f>CONCATENATE("M 19 ",O38)</f>
+        <f>CONCATENATE("M 18 ",O22)</f>
       </c>
     </row>
     <row r="139">
@@ -13555,7 +13549,7 @@
     </row>
     <row r="145">
       <c r="A145" s="14" t="str">
-        <f>CONCATENATE("M 8 ",G62)</f>
+        <f>CONCATENATE("M 6 ",G46)</f>
       </c>
       <c r="B145" s="18"/>
       <c r="C145" s="18"/>
@@ -13563,10 +13557,10 @@
       <c r="E145" s="18"/>
       <c r="F145" s="18"/>
       <c r="G145" s="14" t="str">
-        <f>CONCATENATE("M 7 ",G54)</f>
+        <f>CONCATENATE("M 5 ",G38)</f>
       </c>
       <c r="I145" s="14" t="str">
-        <f>CONCATENATE("M 22 ",O62)</f>
+        <f>CONCATENATE("M 21 ",O46)</f>
       </c>
       <c r="J145" s="18"/>
       <c r="K145" s="18"/>
@@ -13574,7 +13568,7 @@
       <c r="M145" s="18"/>
       <c r="N145" s="18"/>
       <c r="O145" s="14" t="str">
-        <f>CONCATENATE("M 21 ",O54)</f>
+        <f>CONCATENATE("M 20 ",O38)</f>
       </c>
     </row>
     <row r="147">
@@ -13639,7 +13633,7 @@
     </row>
     <row r="153">
       <c r="A153" s="14" t="str">
-        <f>CONCATENATE("M 10 ",G78)</f>
+        <f>CONCATENATE("M 8 ",G62)</f>
       </c>
       <c r="B153" s="18"/>
       <c r="C153" s="18"/>
@@ -13647,10 +13641,10 @@
       <c r="E153" s="18"/>
       <c r="F153" s="18"/>
       <c r="G153" s="14" t="str">
-        <f>CONCATENATE("M 9 ",G70)</f>
+        <f>CONCATENATE("M 7 ",G54)</f>
       </c>
       <c r="I153" s="14" t="str">
-        <f>CONCATENATE("M 24 ",O78)</f>
+        <f>CONCATENATE("M 23 ",O62)</f>
       </c>
       <c r="J153" s="18"/>
       <c r="K153" s="18"/>
@@ -13658,7 +13652,7 @@
       <c r="M153" s="18"/>
       <c r="N153" s="18"/>
       <c r="O153" s="14" t="str">
-        <f>CONCATENATE("M 23 ",O70)</f>
+        <f>CONCATENATE("M 22 ",O54)</f>
       </c>
     </row>
     <row r="155">
@@ -13723,7 +13717,7 @@
     </row>
     <row r="161">
       <c r="A161" s="14" t="str">
-        <f>CONCATENATE("M 12 ",G94)</f>
+        <f>CONCATENATE("M 10 ",G78)</f>
       </c>
       <c r="B161" s="18"/>
       <c r="C161" s="18"/>
@@ -13731,10 +13725,10 @@
       <c r="E161" s="18"/>
       <c r="F161" s="18"/>
       <c r="G161" s="14" t="str">
-        <f>CONCATENATE("M 11 ",G86)</f>
+        <f>CONCATENATE("M 9 ",G70)</f>
       </c>
       <c r="I161" s="14" t="str">
-        <f>CONCATENATE("M 26 ",O94)</f>
+        <f>CONCATENATE("M 25 ",O78)</f>
       </c>
       <c r="J161" s="18"/>
       <c r="K161" s="18"/>
@@ -13742,7 +13736,7 @@
       <c r="M161" s="18"/>
       <c r="N161" s="18"/>
       <c r="O161" s="14" t="str">
-        <f>CONCATENATE("M 25 ",O86)</f>
+        <f>CONCATENATE("M 24 ",O70)</f>
       </c>
     </row>
     <row r="163">
@@ -13807,7 +13801,7 @@
     </row>
     <row r="169">
       <c r="A169" s="14" t="str">
-        <f>CONCATENATE("M 14 ",G110)</f>
+        <f>CONCATENATE("M 12 ",G94)</f>
       </c>
       <c r="B169" s="18"/>
       <c r="C169" s="18"/>
@@ -13815,10 +13809,10 @@
       <c r="E169" s="18"/>
       <c r="F169" s="18"/>
       <c r="G169" s="14" t="str">
-        <f>CONCATENATE("M 13 ",G102)</f>
+        <f>CONCATENATE("M 11 ",G86)</f>
       </c>
       <c r="I169" s="14" t="str">
-        <f>CONCATENATE("M 28 ",O110)</f>
+        <f>CONCATENATE("M 27 ",O94)</f>
       </c>
       <c r="J169" s="18"/>
       <c r="K169" s="18"/>
@@ -13826,7 +13820,7 @@
       <c r="M169" s="18"/>
       <c r="N169" s="18"/>
       <c r="O169" s="14" t="str">
-        <f>CONCATENATE("M 27 ",O102)</f>
+        <f>CONCATENATE("M 26 ",O86)</f>
       </c>
     </row>
     <row r="171">
@@ -13891,7 +13885,7 @@
     </row>
     <row r="177">
       <c r="A177" s="14" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
+        <f>CONCATENATE("M 14 ",G110)</f>
       </c>
       <c r="B177" s="18"/>
       <c r="C177" s="18"/>
@@ -13899,10 +13893,10 @@
       <c r="E177" s="18"/>
       <c r="F177" s="18"/>
       <c r="G177" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
+        <f>CONCATENATE("M 13 ",G102)</f>
       </c>
       <c r="I177" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
+        <f>CONCATENATE("M 29 ",O110)</f>
       </c>
       <c r="J177" s="18"/>
       <c r="K177" s="18"/>
@@ -13910,7 +13904,7 @@
       <c r="M177" s="18"/>
       <c r="N177" s="18"/>
       <c r="O177" s="14" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
+        <f>CONCATENATE("M 28 ",O102)</f>
       </c>
     </row>
     <row r="179">
@@ -13975,7 +13969,7 @@
     </row>
     <row r="190">
       <c r="A190" s="14" t="str">
-        <f>CONCATENATE("M 30 ",G131)</f>
+        <f>CONCATENATE("M 32 ",G139)</f>
       </c>
       <c r="B190" s="18"/>
       <c r="C190" s="18"/>
@@ -13983,10 +13977,10 @@
       <c r="E190" s="18"/>
       <c r="F190" s="18"/>
       <c r="G190" s="14" t="str">
-        <f>CONCATENATE("M 29 ",G123)</f>
+        <f>CONCATENATE("M 31 ",G131)</f>
       </c>
       <c r="I190" s="14" t="str">
-        <f>CONCATENATE("M 38 ",O131)</f>
+        <f>CONCATENATE("M 39 ",O139)</f>
       </c>
       <c r="J190" s="18"/>
       <c r="K190" s="18"/>
@@ -13994,7 +13988,7 @@
       <c r="M190" s="18"/>
       <c r="N190" s="18"/>
       <c r="O190" s="14" t="str">
-        <f>CONCATENATE("M 37 ",O123)</f>
+        <f>CONCATENATE("M 38 ",O131)</f>
       </c>
     </row>
     <row r="192">
@@ -14059,7 +14053,7 @@
     </row>
     <row r="198">
       <c r="A198" s="14" t="str">
-        <f>CONCATENATE("M 32 ",G147)</f>
+        <f>CONCATENATE("M 34 ",G155)</f>
       </c>
       <c r="B198" s="18"/>
       <c r="C198" s="18"/>
@@ -14067,10 +14061,10 @@
       <c r="E198" s="18"/>
       <c r="F198" s="18"/>
       <c r="G198" s="14" t="str">
-        <f>CONCATENATE("M 31 ",G139)</f>
+        <f>CONCATENATE("M 33 ",G147)</f>
       </c>
       <c r="I198" s="14" t="str">
-        <f>CONCATENATE("M 40 ",O147)</f>
+        <f>CONCATENATE("M 41 ",O155)</f>
       </c>
       <c r="J198" s="18"/>
       <c r="K198" s="18"/>
@@ -14078,7 +14072,7 @@
       <c r="M198" s="18"/>
       <c r="N198" s="18"/>
       <c r="O198" s="14" t="str">
-        <f>CONCATENATE("M 39 ",O139)</f>
+        <f>CONCATENATE("M 40 ",O147)</f>
       </c>
     </row>
     <row r="200">
@@ -14143,7 +14137,7 @@
     </row>
     <row r="206">
       <c r="A206" s="14" t="str">
-        <f>CONCATENATE("M 34 ",G163)</f>
+        <f>CONCATENATE("M 36 ",G171)</f>
       </c>
       <c r="B206" s="18"/>
       <c r="C206" s="18"/>
@@ -14151,10 +14145,10 @@
       <c r="E206" s="18"/>
       <c r="F206" s="18"/>
       <c r="G206" s="14" t="str">
-        <f>CONCATENATE("M 33 ",G155)</f>
+        <f>CONCATENATE("M 35 ",G163)</f>
       </c>
       <c r="I206" s="14" t="str">
-        <f>CONCATENATE("M 42 ",O163)</f>
+        <f>CONCATENATE("M 43 ",O171)</f>
       </c>
       <c r="J206" s="18"/>
       <c r="K206" s="18"/>
@@ -14162,7 +14156,7 @@
       <c r="M206" s="18"/>
       <c r="N206" s="18"/>
       <c r="O206" s="14" t="str">
-        <f>CONCATENATE("M 41 ",O155)</f>
+        <f>CONCATENATE("M 42 ",O163)</f>
       </c>
     </row>
     <row r="208">
@@ -14227,7 +14221,7 @@
     </row>
     <row r="214">
       <c r="A214" s="14" t="str">
-        <f>CONCATENATE("M 36 ",G179)</f>
+        <f>CONCATENATE("M 15 ",G118)</f>
       </c>
       <c r="B214" s="18"/>
       <c r="C214" s="18"/>
@@ -14235,10 +14229,10 @@
       <c r="E214" s="18"/>
       <c r="F214" s="18"/>
       <c r="G214" s="14" t="str">
-        <f>CONCATENATE("M 35 ",G171)</f>
+        <f>CONCATENATE("M 37 ",G179)</f>
       </c>
       <c r="I214" s="14" t="str">
-        <f>CONCATENATE("M 44 ",O179)</f>
+        <f>CONCATENATE("M 30 ",O118)</f>
       </c>
       <c r="J214" s="18"/>
       <c r="K214" s="18"/>
@@ -14246,7 +14240,7 @@
       <c r="M214" s="18"/>
       <c r="N214" s="18"/>
       <c r="O214" s="14" t="str">
-        <f>CONCATENATE("M 43 ",O171)</f>
+        <f>CONCATENATE("M 44 ",O179)</f>
       </c>
     </row>
     <row r="216">
@@ -14601,8 +14595,8 @@
     <mergeCell ref="I98:O98"/>
     <mergeCell ref="A106:G106"/>
     <mergeCell ref="I106:O106"/>
-    <mergeCell ref="A119:G119"/>
-    <mergeCell ref="I119:O119"/>
+    <mergeCell ref="A114:G114"/>
+    <mergeCell ref="I114:O114"/>
     <mergeCell ref="A127:G127"/>
     <mergeCell ref="I127:O127"/>
     <mergeCell ref="A135:G135"/>
@@ -14638,10 +14632,10 @@
   <rowBreaks count="6" manualBreakCount="6">
     <brk id="41" max="16383" man="true"/>
     <brk id="81" max="16383" man="true"/>
-    <brk id="118" max="16383" man="true"/>
-    <brk id="158" max="16383" man="true"/>
-    <brk id="195" max="16383" man="true"/>
-    <brk id="232" max="16383" man="true"/>
+    <brk id="126" max="16383" man="true"/>
+    <brk id="166" max="16383" man="true"/>
+    <brk id="203" max="16383" man="true"/>
+    <brk id="245" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="true"/>
@@ -14717,7 +14711,7 @@
         <f>"4. " &amp; data!$B$6</f>
       </c>
       <c r="G8" s="21">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -14799,7 +14793,7 @@
         <f>"1. " &amp; data!$B$10</f>
       </c>
       <c r="G16" s="21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -14879,7 +14873,7 @@
     <row r="24">
       <c r="A24" s="22"/>
       <c r="G24" s="21">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -14965,7 +14959,7 @@
         <f>"2. " &amp; data!$B$20</f>
       </c>
       <c r="G32" s="21">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
@@ -15115,7 +15109,7 @@
     <row r="8">
       <c r="A8" s="22"/>
       <c r="G8" s="21">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -15199,7 +15193,7 @@
         <f>"2. " &amp; data!$B$35</f>
       </c>
       <c r="G16" s="21">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -15279,7 +15273,7 @@
         <f>'data'!$A$42</f>
       </c>
       <c r="G24" s="21">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -15332,16 +15326,18 @@
       <c r="A29" s="24" t="str">
         <f>'data'!$A$45</f>
       </c>
+      <c r="C29" s="23" t="str">
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
+      </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30">
       <c r="A30" s="25" t="str">
         <f>"1. " &amp; data!$B$43</f>
       </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
+      <c r="D30" s="22"/>
+      <c r="E30" s="21">
+        <v>15</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -15349,35 +15345,27 @@
       <c r="A31" s="26" t="str">
         <f>"2. " &amp; data!$B$44</f>
       </c>
-      <c r="F31" s="22"/>
-      <c r="G31" s="20"/>
+      <c r="C31" s="23" t="str">
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="20"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32">
       <c r="A32" s="27" t="str">
         <f>"3. " &amp; data!$B$45</f>
       </c>
-      <c r="G32" s="21">
-        <v>36</v>
-      </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
     </row>
     <row r="33">
       <c r="A33" s="22"/>
-      <c r="G33" s="20"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="str">
         <f>'data'!$A$48</f>
       </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
-      </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="20"/>
     </row>
     <row r="35">
       <c r="A35" s="25" t="str">

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -98,43 +98,607 @@
     <t>CLARK</t>
   </si>
   <si>
+    <t>Elijah Taylor</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>TAYLOR</t>
+  </si>
+  <si>
+    <t>Fyodor Dostoevsky</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>DOSTOEVSKY</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>LANNISTER</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
+    <t>Yann Martel</t>
+  </si>
+  <si>
+    <t>MARTEL</t>
+  </si>
+  <si>
+    <t>Gabriel Thomas</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>THOMAS</t>
+  </si>
+  <si>
+    <t>Kurt Vonnegut</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>VONNEGUT</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Aaron Thompson</t>
+  </si>
+  <si>
+    <t>THOMPSON</t>
+  </si>
+  <si>
+    <t>Yosef Hill</t>
+  </si>
+  <si>
+    <t>HILL</t>
+  </si>
+  <si>
+    <t>Mary Shelley</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>SHELLEY</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Albus Dumbledore</t>
+  </si>
+  <si>
+    <t>DUMBLEDORE</t>
+  </si>
+  <si>
+    <t>Jackson Harris</t>
+  </si>
+  <si>
+    <t>Team Kappa</t>
+  </si>
+  <si>
+    <t>HARRIS</t>
+  </si>
+  <si>
+    <t>Oscar Wilde</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>WILDE</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
+    <t>Uriel Wright</t>
+  </si>
+  <si>
+    <t>WRIGHT</t>
+  </si>
+  <si>
+    <t>Emily Bronte</t>
+  </si>
+  <si>
+    <t>BRONTE</t>
+  </si>
+  <si>
+    <t>Philip K Dick</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Pool F</t>
+  </si>
+  <si>
+    <t>Ygritte</t>
+  </si>
+  <si>
+    <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>George Orwell</t>
+  </si>
+  <si>
+    <t>ORWELL</t>
+  </si>
+  <si>
+    <t>Quentin Blake</t>
+  </si>
+  <si>
+    <t>Team Rho</t>
+  </si>
+  <si>
+    <t>BLAKE</t>
+  </si>
+  <si>
+    <t>Pool G</t>
+  </si>
+  <si>
+    <t>Kaden Martin</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>William Wright</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>Sylvia Plath</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>PLATH</t>
+  </si>
+  <si>
+    <t>Pool H</t>
+  </si>
+  <si>
+    <t>Xavier Lopez</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>Herman Melville</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>MELVILLE</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Pool I</t>
+  </si>
+  <si>
+    <t>Paul Hall</t>
+  </si>
+  <si>
+    <t>HALL</t>
+  </si>
+  <si>
+    <t>Caleb Wilson</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>Pool J</t>
+  </si>
+  <si>
+    <t>Dylan Moore</t>
+  </si>
+  <si>
+    <t>MOORE</t>
+  </si>
+  <si>
+    <t>Sebastian Allen</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>ALLEN</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Pool K</t>
+  </si>
+  <si>
+    <t>Ulysses Hernandez</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>Charles Dickens</t>
+  </si>
+  <si>
+    <t>DICKENS</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>Pool L</t>
+  </si>
+  <si>
+    <t>Daniel Defoe</t>
+  </si>
+  <si>
+    <t>DEFOE</t>
+  </si>
+  <si>
+    <t>Parker Lewis</t>
+  </si>
+  <si>
+    <t>LEWIS</t>
+  </si>
+  <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>Pool M</t>
+  </si>
+  <si>
+    <t>Zachary Adams</t>
+  </si>
+  <si>
+    <t>ADAMS</t>
+  </si>
+  <si>
+    <t>Cersei Lannister</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>Pool N</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>Quirinus Quirrell</t>
+  </si>
+  <si>
+    <t>QUIRRELL</t>
+  </si>
+  <si>
+    <t>Pool O</t>
+  </si>
+  <si>
+    <t>Michael Lewis</t>
+  </si>
+  <si>
+    <t>Arthur Conan</t>
+  </si>
+  <si>
+    <t>CONAN</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>Pool P</t>
+  </si>
+  <si>
+    <t>Luke Rodriguez</t>
+  </si>
+  <si>
+    <t>Team Beta</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>Robert Young</t>
+  </si>
+  <si>
+    <t>YOUNG</t>
+  </si>
+  <si>
+    <t>Nathaniel Hawthorne</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>HAWTHORNE</t>
+  </si>
+  <si>
+    <t>Pool Q</t>
+  </si>
+  <si>
+    <t>Steven Hernandez</t>
+  </si>
+  <si>
+    <t>Isaac White</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>Lewis Carroll</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>CARROLL</t>
+  </si>
+  <si>
+    <t>Pool R</t>
+  </si>
+  <si>
+    <t>Liam Thompson</t>
+  </si>
+  <si>
+    <t>Mason Martinez</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>Xavier Herbert</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>HERBERT</t>
+  </si>
+  <si>
+    <t>Pool S</t>
+  </si>
+  <si>
+    <t>Nolan Clark</t>
+  </si>
+  <si>
+    <t>Hudson Jackson</t>
+  </si>
+  <si>
+    <t>JACKSON</t>
+  </si>
+  <si>
+    <t>Ursula K Le Guin</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>LE GUIN</t>
+  </si>
+  <si>
+    <t>Pool T</t>
+  </si>
+  <si>
+    <t>Victor Lopez</t>
+  </si>
+  <si>
+    <t>William Hill</t>
+  </si>
+  <si>
+    <t>William Shakespeare</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>SHAKESPEARE</t>
+  </si>
+  <si>
+    <t>Pool U</t>
+  </si>
+  <si>
     <t>Xavier Scott</t>
   </si>
   <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
     <t>SCOTT</t>
   </si>
   <si>
-    <t>Parker Lewis</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
-    <t>LEWIS</t>
+    <t>Isaac Asimov</t>
+  </si>
+  <si>
+    <t>ASIMOV</t>
+  </si>
+  <si>
+    <t>Ray Bradbury</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>BRADBURY</t>
+  </si>
+  <si>
+    <t>Pool V</t>
+  </si>
+  <si>
+    <t>Vincent King</t>
+  </si>
+  <si>
+    <t>KING</t>
+  </si>
+  <si>
+    <t>Jane Austen</t>
+  </si>
+  <si>
+    <t>AUSTEN</t>
+  </si>
+  <si>
+    <t>Thomas Hardy</t>
+  </si>
+  <si>
+    <t>HARDY</t>
+  </si>
+  <si>
+    <t>Pool W</t>
+  </si>
+  <si>
+    <t>Oliver Walker</t>
+  </si>
+  <si>
+    <t>WALKER</t>
+  </si>
+  <si>
+    <t>Finn Anderson</t>
+  </si>
+  <si>
+    <t>ANDERSON</t>
   </si>
   <si>
     <t>Neville Longbottom</t>
   </si>
   <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
     <t>LONGBOTTOM</t>
   </si>
   <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>HALL</t>
-  </si>
-  <si>
-    <t>Nolan Clark</t>
+    <t>Pool X</t>
+  </si>
+  <si>
+    <t>Quentin Allen</t>
+  </si>
+  <si>
+    <t>Quinn Walker</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Pool Y</t>
+  </si>
+  <si>
+    <t>Thomas King</t>
+  </si>
+  <si>
+    <t>Tristan Young</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Pool Z</t>
+  </si>
+  <si>
+    <t>Bram Stoker</t>
+  </si>
+  <si>
+    <t>STOKER</t>
+  </si>
+  <si>
+    <t>Ryan Hall</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Pool AA</t>
+  </si>
+  <si>
+    <t>Owen Rodriguez</t>
+  </si>
+  <si>
+    <t>Virginia Woolf</t>
+  </si>
+  <si>
+    <t>WOOLF</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>Pool BB</t>
+  </si>
+  <si>
+    <t>Benjamin Evans</t>
+  </si>
+  <si>
+    <t>EVANS</t>
+  </si>
+  <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
   </si>
   <si>
     <t>Frodo Baggins</t>
@@ -143,133 +707,7 @@
     <t>BAGGINS</t>
   </si>
   <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Zachary Adams</t>
-  </si>
-  <si>
-    <t>ADAMS</t>
-  </si>
-  <si>
-    <t>Daniel Defoe</t>
-  </si>
-  <si>
-    <t>DEFOE</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Kaden Martin</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>Robert Young</t>
-  </si>
-  <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
-    <t>YOUNG</t>
-  </si>
-  <si>
-    <t>Katniss Everdeen</t>
-  </si>
-  <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
-    <t>EVERDEEN</t>
-  </si>
-  <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Arthur Conan</t>
-  </si>
-  <si>
-    <t>CONAN</t>
-  </si>
-  <si>
-    <t>Caleb Wilson</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Pool F</t>
-  </si>
-  <si>
-    <t>Albus Dumbledore</t>
-  </si>
-  <si>
-    <t>DUMBLEDORE</t>
-  </si>
-  <si>
-    <t>William Wright</t>
-  </si>
-  <si>
-    <t>WRIGHT</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Pool G</t>
-  </si>
-  <si>
-    <t>Oliver Walker</t>
-  </si>
-  <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>WALKER</t>
-  </si>
-  <si>
-    <t>Cersei Lannister</t>
-  </si>
-  <si>
-    <t>LANNISTER</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>Pool H</t>
+    <t>Pool CC</t>
   </si>
   <si>
     <t>Yosef Green</t>
@@ -278,129 +716,6 @@
     <t>GREEN</t>
   </si>
   <si>
-    <t>Quinn Walker</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>Pool I</t>
-  </si>
-  <si>
-    <t>Owen Rodriguez</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Pool J</t>
-  </si>
-  <si>
-    <t>Emily Bronte</t>
-  </si>
-  <si>
-    <t>BRONTE</t>
-  </si>
-  <si>
-    <t>Sebastian Allen</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>ALLEN</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>Pool K</t>
-  </si>
-  <si>
-    <t>Quentin Allen</t>
-  </si>
-  <si>
-    <t>Team Beta</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>Pool L</t>
-  </si>
-  <si>
-    <t>Benjamin Evans</t>
-  </si>
-  <si>
-    <t>EVANS</t>
-  </si>
-  <si>
-    <t>Tristan Young</t>
-  </si>
-  <si>
-    <t>Team Kappa</t>
-  </si>
-  <si>
-    <t>Quirinus Quirrell</t>
-  </si>
-  <si>
-    <t>Team Rho</t>
-  </si>
-  <si>
-    <t>QUIRRELL</t>
-  </si>
-  <si>
-    <t>Pool M</t>
-  </si>
-  <si>
-    <t>Vincent King</t>
-  </si>
-  <si>
-    <t>KING</t>
-  </si>
-  <si>
     <t>Jon Snow</t>
   </si>
   <si>
@@ -410,340 +725,25 @@
     <t>Ron Weasley</t>
   </si>
   <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
     <t>WEASLEY</t>
   </si>
   <si>
-    <t>Pool N</t>
+    <t>Pool DD</t>
+  </si>
+  <si>
+    <t>Nathan Lee</t>
+  </si>
+  <si>
+    <t>LEE</t>
   </si>
   <si>
     <t>Bilbo Baggins</t>
   </si>
   <si>
-    <t>Ryan Hall</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
     <t>Samwise Gamgee</t>
   </si>
   <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
     <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>Pool O</t>
-  </si>
-  <si>
-    <t>Michael Lewis</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>Pool P</t>
-  </si>
-  <si>
-    <t>Luke Rodriguez</t>
-  </si>
-  <si>
-    <t>Dylan Moore</t>
-  </si>
-  <si>
-    <t>MOORE</t>
-  </si>
-  <si>
-    <t>Fyodor Dostoevsky</t>
-  </si>
-  <si>
-    <t>DOSTOEVSKY</t>
-  </si>
-  <si>
-    <t>Pool Q</t>
-  </si>
-  <si>
-    <t>Uriel Wright</t>
-  </si>
-  <si>
-    <t>Xavier Lopez</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>Virginia Woolf</t>
-  </si>
-  <si>
-    <t>WOOLF</t>
-  </si>
-  <si>
-    <t>Pool R</t>
-  </si>
-  <si>
-    <t>Aaron Thompson</t>
-  </si>
-  <si>
-    <t>THOMPSON</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Kurt Vonnegut</t>
-  </si>
-  <si>
-    <t>VONNEGUT</t>
-  </si>
-  <si>
-    <t>Pool S</t>
-  </si>
-  <si>
-    <t>Ulysses Hernandez</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>William Hill</t>
-  </si>
-  <si>
-    <t>HILL</t>
-  </si>
-  <si>
-    <t>Lewis Carroll</t>
-  </si>
-  <si>
-    <t>CARROLL</t>
-  </si>
-  <si>
-    <t>Pool T</t>
-  </si>
-  <si>
-    <t>Yann Martel</t>
-  </si>
-  <si>
-    <t>MARTEL</t>
-  </si>
-  <si>
-    <t>Mason Martinez</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>Mary Shelley</t>
-  </si>
-  <si>
-    <t>SHELLEY</t>
-  </si>
-  <si>
-    <t>Pool U</t>
-  </si>
-  <si>
-    <t>Ygritte</t>
-  </si>
-  <si>
-    <t>YGRITTE</t>
-  </si>
-  <si>
-    <t>Charles Dickens</t>
-  </si>
-  <si>
-    <t>DICKENS</t>
-  </si>
-  <si>
-    <t>Xavier Herbert</t>
-  </si>
-  <si>
-    <t>HERBERT</t>
-  </si>
-  <si>
-    <t>Pool V</t>
-  </si>
-  <si>
-    <t>Thomas King</t>
-  </si>
-  <si>
-    <t>Gabriel Thomas</t>
-  </si>
-  <si>
-    <t>THOMAS</t>
-  </si>
-  <si>
-    <t>Oscar Wilde</t>
-  </si>
-  <si>
-    <t>WILDE</t>
-  </si>
-  <si>
-    <t>Pool W</t>
-  </si>
-  <si>
-    <t>Elijah Taylor</t>
-  </si>
-  <si>
-    <t>TAYLOR</t>
-  </si>
-  <si>
-    <t>George Orwell</t>
-  </si>
-  <si>
-    <t>ORWELL</t>
-  </si>
-  <si>
-    <t>Ursula K Le Guin</t>
-  </si>
-  <si>
-    <t>LE GUIN</t>
-  </si>
-  <si>
-    <t>Pool X</t>
-  </si>
-  <si>
-    <t>Yosef Hill</t>
-  </si>
-  <si>
-    <t>Isaac White</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>Philip K Dick</t>
-  </si>
-  <si>
-    <t>Pool Y</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Isaac Asimov</t>
-  </si>
-  <si>
-    <t>ASIMOV</t>
-  </si>
-  <si>
-    <t>William Shakespeare</t>
-  </si>
-  <si>
-    <t>SHAKESPEARE</t>
-  </si>
-  <si>
-    <t>Pool Z</t>
-  </si>
-  <si>
-    <t>Victor Lopez</t>
-  </si>
-  <si>
-    <t>Jackson Harris</t>
-  </si>
-  <si>
-    <t>HARRIS</t>
-  </si>
-  <si>
-    <t>Quentin Blake</t>
-  </si>
-  <si>
-    <t>BLAKE</t>
-  </si>
-  <si>
-    <t>Pool AA</t>
-  </si>
-  <si>
-    <t>Liam Thompson</t>
-  </si>
-  <si>
-    <t>Jane Austen</t>
-  </si>
-  <si>
-    <t>AUSTEN</t>
-  </si>
-  <si>
-    <t>Ray Bradbury</t>
-  </si>
-  <si>
-    <t>BRADBURY</t>
-  </si>
-  <si>
-    <t>Pool BB</t>
-  </si>
-  <si>
-    <t>Bram Stoker</t>
-  </si>
-  <si>
-    <t>STOKER</t>
-  </si>
-  <si>
-    <t>Hudson Jackson</t>
-  </si>
-  <si>
-    <t>JACKSON</t>
-  </si>
-  <si>
-    <t>Sylvia Plath</t>
-  </si>
-  <si>
-    <t>PLATH</t>
-  </si>
-  <si>
-    <t>Pool CC</t>
-  </si>
-  <si>
-    <t>Steven Hernandez</t>
-  </si>
-  <si>
-    <t>Herman Melville</t>
-  </si>
-  <si>
-    <t>MELVILLE</t>
-  </si>
-  <si>
-    <t>Thomas Hardy</t>
-  </si>
-  <si>
-    <t>HARDY</t>
-  </si>
-  <si>
-    <t>Pool DD</t>
-  </si>
-  <si>
-    <t>Nathan Lee</t>
-  </si>
-  <si>
-    <t>LEE</t>
-  </si>
-  <si>
-    <t>Finn Anderson</t>
-  </si>
-  <si>
-    <t>ANDERSON</t>
-  </si>
-  <si>
-    <t>Nathaniel Hawthorne</t>
-  </si>
-  <si>
-    <t>HAWTHORNE</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -1973,10 +1973,10 @@
         <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -1984,388 +1984,388 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="D36" t="s">
         <v>109</v>
@@ -2379,7 +2379,7 @@
         <v>111</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
         <v>112</v>
@@ -2393,10 +2393,10 @@
         <v>113</v>
       </c>
       <c r="C38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" t="s">
         <v>114</v>
-      </c>
-      <c r="D38" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="39">
@@ -2407,175 +2407,175 @@
         <v>115</v>
       </c>
       <c r="C39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" t="s">
         <v>116</v>
-      </c>
-      <c r="D39" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" t="s">
         <v>118</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" t="s">
         <v>119</v>
-      </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" t="s">
         <v>126</v>
       </c>
-      <c r="B44" t="s">
-        <v>128</v>
-      </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="D45" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B46" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="D46" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" t="s">
+        <v>132</v>
+      </c>
+      <c r="C47" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" t="s">
         <v>133</v>
-      </c>
-      <c r="B47" t="s">
-        <v>135</v>
-      </c>
-      <c r="C47" t="s">
-        <v>129</v>
-      </c>
-      <c r="D47" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" t="s">
+        <v>137</v>
+      </c>
+      <c r="C49" t="s">
+        <v>138</v>
+      </c>
+      <c r="D49" t="s">
         <v>139</v>
-      </c>
-      <c r="B49" t="s">
-        <v>140</v>
-      </c>
-      <c r="C49" t="s">
-        <v>104</v>
-      </c>
-      <c r="D49" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" t="s">
         <v>141</v>
-      </c>
-      <c r="C50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B51" t="s">
+        <v>142</v>
+      </c>
+      <c r="C51" t="s">
         <v>143</v>
-      </c>
-      <c r="C51" t="s">
-        <v>24</v>
       </c>
       <c r="D51" t="s">
         <v>144</v>
@@ -2589,10 +2589,10 @@
         <v>146</v>
       </c>
       <c r="C52" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53">
@@ -2603,7 +2603,7 @@
         <v>147</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="D53" t="s">
         <v>148</v>
@@ -2617,35 +2617,35 @@
         <v>149</v>
       </c>
       <c r="C54" t="s">
-        <v>41</v>
+        <v>150</v>
       </c>
       <c r="D54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="D55" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B56" t="s">
         <v>154</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D56" t="s">
         <v>155</v>
@@ -2653,41 +2653,41 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B57" t="s">
         <v>156</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="D57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C58" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D58" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B59" t="s">
         <v>161</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="D59" t="s">
         <v>162</v>
@@ -2695,55 +2695,55 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B60" t="s">
         <v>163</v>
       </c>
       <c r="C60" t="s">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="D60" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B61" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C61" t="s">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="D61" t="s">
-        <v>167</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B62" t="s">
         <v>168</v>
       </c>
       <c r="C62" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B63" t="s">
+        <v>169</v>
+      </c>
+      <c r="C63" t="s">
         <v>170</v>
-      </c>
-      <c r="C63" t="s">
-        <v>66</v>
       </c>
       <c r="D63" t="s">
         <v>171</v>
@@ -2757,7 +2757,7 @@
         <v>173</v>
       </c>
       <c r="C64" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D64" t="s">
         <v>174</v>
@@ -2771,7 +2771,7 @@
         <v>175</v>
       </c>
       <c r="C65" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="D65" t="s">
         <v>176</v>
@@ -2785,175 +2785,175 @@
         <v>177</v>
       </c>
       <c r="C66" t="s">
-        <v>75</v>
+        <v>178</v>
       </c>
       <c r="D66" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B67" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C67" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="D67" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B68" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C68" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D68" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B69" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C69" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B70" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C70" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B71" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C71" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="D71" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B72" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D72" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B73" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C73" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="D73" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B74" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C74" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="D74" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B75" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C75" t="s">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D75" t="s">
-        <v>67</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B76" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C76" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="D76" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B77" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C77" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="D77" t="s">
-        <v>201</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B78" t="s">
         <v>202</v>
       </c>
       <c r="C78" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="D78" t="s">
         <v>203</v>
@@ -2967,10 +2967,10 @@
         <v>205</v>
       </c>
       <c r="C79" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="D79" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80">
@@ -2978,13 +2978,13 @@
         <v>204</v>
       </c>
       <c r="B80" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C80" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D80" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81">
@@ -2995,7 +2995,7 @@
         <v>208</v>
       </c>
       <c r="C81" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="D81" t="s">
         <v>209</v>
@@ -3009,10 +3009,10 @@
         <v>211</v>
       </c>
       <c r="C82" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="D82" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="83">
@@ -3023,7 +3023,7 @@
         <v>212</v>
       </c>
       <c r="C83" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="D83" t="s">
         <v>213</v>
@@ -3037,7 +3037,7 @@
         <v>214</v>
       </c>
       <c r="C84" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
         <v>215</v>
@@ -3051,7 +3051,7 @@
         <v>217</v>
       </c>
       <c r="C85" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="D85" t="s">
         <v>218</v>
@@ -3065,7 +3065,7 @@
         <v>219</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="D86" t="s">
         <v>220</v>
@@ -3079,7 +3079,7 @@
         <v>221</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="D87" t="s">
         <v>222</v>
@@ -3096,7 +3096,7 @@
         <v>21</v>
       </c>
       <c r="D88" t="s">
-        <v>160</v>
+        <v>225</v>
       </c>
     </row>
     <row r="89">
@@ -3104,13 +3104,13 @@
         <v>223</v>
       </c>
       <c r="B89" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C89" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="D89" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="90">
@@ -3118,52 +3118,52 @@
         <v>223</v>
       </c>
       <c r="B90" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C90" t="s">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="D90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B91" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="D91" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B92" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="D92" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B93" t="s">
         <v>234</v>
       </c>
       <c r="C93" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="D93" t="s">
         <v>235</v>

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -98,160 +98,643 @@
     <t>CLARK</t>
   </si>
   <si>
+    <t>Oliver Walker</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>WALKER</t>
+  </si>
+  <si>
+    <t>Mason Martinez</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
+    <t>Liam Thompson</t>
+  </si>
+  <si>
+    <t>Team Beta</t>
+  </si>
+  <si>
+    <t>THOMPSON</t>
+  </si>
+  <si>
+    <t>Tristan Young</t>
+  </si>
+  <si>
+    <t>Team Kappa</t>
+  </si>
+  <si>
+    <t>YOUNG</t>
+  </si>
+  <si>
+    <t>Virginia Woolf</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>WOOLF</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Steven Hernandez</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>Ryan Hall</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>HALL</t>
+  </si>
+  <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Gabriel Thomas</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>THOMAS</t>
+  </si>
+  <si>
+    <t>Lewis Carroll</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>CARROLL</t>
+  </si>
+  <si>
+    <t>Ygritte</t>
+  </si>
+  <si>
+    <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
+    <t>Quentin Allen</t>
+  </si>
+  <si>
+    <t>ALLEN</t>
+  </si>
+  <si>
+    <t>Parker Lewis</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>LEWIS</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Pool F</t>
+  </si>
+  <si>
+    <t>Caleb Wilson</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>Yosef Hill</t>
+  </si>
+  <si>
+    <t>HILL</t>
+  </si>
+  <si>
+    <t>Yann Martel</t>
+  </si>
+  <si>
+    <t>MARTEL</t>
+  </si>
+  <si>
+    <t>Pool G</t>
+  </si>
+  <si>
+    <t>Aaron Thompson</t>
+  </si>
+  <si>
+    <t>Nolan Clark</t>
+  </si>
+  <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>Pool H</t>
+  </si>
+  <si>
+    <t>Isaac White</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>Nathaniel Hawthorne</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>HAWTHORNE</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Pool I</t>
+  </si>
+  <si>
+    <t>Uriel Wright</t>
+  </si>
+  <si>
+    <t>WRIGHT</t>
+  </si>
+  <si>
+    <t>Quentin Blake</t>
+  </si>
+  <si>
+    <t>Team Rho</t>
+  </si>
+  <si>
+    <t>BLAKE</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>Pool J</t>
+  </si>
+  <si>
+    <t>Xavier Scott</t>
+  </si>
+  <si>
+    <t>SCOTT</t>
+  </si>
+  <si>
+    <t>Isaac Asimov</t>
+  </si>
+  <si>
+    <t>ASIMOV</t>
+  </si>
+  <si>
+    <t>Xavier Herbert</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>HERBERT</t>
+  </si>
+  <si>
+    <t>Pool K</t>
+  </si>
+  <si>
+    <t>Victor Lopez</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>Charles Dickens</t>
+  </si>
+  <si>
+    <t>DICKENS</t>
+  </si>
+  <si>
+    <t>Frodo Baggins</t>
+  </si>
+  <si>
+    <t>BAGGINS</t>
+  </si>
+  <si>
+    <t>Pool L</t>
+  </si>
+  <si>
     <t>Elijah Taylor</t>
   </si>
   <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
     <t>TAYLOR</t>
   </si>
   <si>
+    <t>Oscar Wilde</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>WILDE</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>Pool M</t>
+  </si>
+  <si>
+    <t>Bram Stoker</t>
+  </si>
+  <si>
+    <t>STOKER</t>
+  </si>
+  <si>
+    <t>Emily Bronte</t>
+  </si>
+  <si>
+    <t>BRONTE</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>Pool N</t>
+  </si>
+  <si>
+    <t>Arthur Conan</t>
+  </si>
+  <si>
+    <t>CONAN</t>
+  </si>
+  <si>
+    <t>George Orwell</t>
+  </si>
+  <si>
+    <t>ORWELL</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>LANNISTER</t>
+  </si>
+  <si>
+    <t>Pool O</t>
+  </si>
+  <si>
+    <t>Michael Lewis</t>
+  </si>
+  <si>
+    <t>Sylvia Plath</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>PLATH</t>
+  </si>
+  <si>
+    <t>Jon Snow</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>Pool P</t>
+  </si>
+  <si>
+    <t>Luke Rodriguez</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>Owen Rodriguez</t>
+  </si>
+  <si>
+    <t>Quirinus Quirrell</t>
+  </si>
+  <si>
+    <t>QUIRRELL</t>
+  </si>
+  <si>
+    <t>Pool Q</t>
+  </si>
+  <si>
+    <t>Finn Anderson</t>
+  </si>
+  <si>
+    <t>ANDERSON</t>
+  </si>
+  <si>
+    <t>Xavier Lopez</t>
+  </si>
+  <si>
+    <t>William Shakespeare</t>
+  </si>
+  <si>
+    <t>SHAKESPEARE</t>
+  </si>
+  <si>
+    <t>Pool R</t>
+  </si>
+  <si>
+    <t>Robert Young</t>
+  </si>
+  <si>
+    <t>Thomas Hardy</t>
+  </si>
+  <si>
+    <t>HARDY</t>
+  </si>
+  <si>
+    <t>Zachary Adams</t>
+  </si>
+  <si>
+    <t>ADAMS</t>
+  </si>
+  <si>
+    <t>Pool S</t>
+  </si>
+  <si>
+    <t>Hudson Jackson</t>
+  </si>
+  <si>
+    <t>JACKSON</t>
+  </si>
+  <si>
+    <t>Mary Shelley</t>
+  </si>
+  <si>
+    <t>SHELLEY</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>Pool T</t>
+  </si>
+  <si>
+    <t>Paul Hall</t>
+  </si>
+  <si>
+    <t>Quinn Walker</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Pool U</t>
+  </si>
+  <si>
+    <t>Dylan Moore</t>
+  </si>
+  <si>
+    <t>MOORE</t>
+  </si>
+  <si>
+    <t>William Wright</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>Pool V</t>
+  </si>
+  <si>
+    <t>Thomas King</t>
+  </si>
+  <si>
+    <t>KING</t>
+  </si>
+  <si>
+    <t>Sebastian Allen</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Pool W</t>
+  </si>
+  <si>
+    <t>Jackson Harris</t>
+  </si>
+  <si>
+    <t>HARRIS</t>
+  </si>
+  <si>
+    <t>Vincent King</t>
+  </si>
+  <si>
+    <t>Albus Dumbledore</t>
+  </si>
+  <si>
+    <t>DUMBLEDORE</t>
+  </si>
+  <si>
+    <t>Pool X</t>
+  </si>
+  <si>
+    <t>William Hill</t>
+  </si>
+  <si>
+    <t>Philip K Dick</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>Pool Y</t>
+  </si>
+  <si>
+    <t>Benjamin Evans</t>
+  </si>
+  <si>
+    <t>EVANS</t>
+  </si>
+  <si>
+    <t>Herman Melville</t>
+  </si>
+  <si>
+    <t>MELVILLE</t>
+  </si>
+  <si>
+    <t>Ursula K Le Guin</t>
+  </si>
+  <si>
+    <t>LE GUIN</t>
+  </si>
+  <si>
+    <t>Pool Z</t>
+  </si>
+  <si>
+    <t>Yosef Green</t>
+  </si>
+  <si>
+    <t>GREEN</t>
+  </si>
+  <si>
+    <t>Daniel Defoe</t>
+  </si>
+  <si>
+    <t>DEFOE</t>
+  </si>
+  <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>Pool AA</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>Jane Austen</t>
+  </si>
+  <si>
+    <t>AUSTEN</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Pool BB</t>
+  </si>
+  <si>
+    <t>Ulysses Hernandez</t>
+  </si>
+  <si>
     <t>Fyodor Dostoevsky</t>
   </si>
   <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
     <t>DOSTOEVSKY</t>
   </si>
   <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>LANNISTER</t>
-  </si>
-  <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Yann Martel</t>
-  </si>
-  <si>
-    <t>MARTEL</t>
-  </si>
-  <si>
-    <t>Gabriel Thomas</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>THOMAS</t>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>Pool CC</t>
   </si>
   <si>
     <t>Kurt Vonnegut</t>
   </si>
   <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
     <t>VONNEGUT</t>
   </si>
   <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Aaron Thompson</t>
-  </si>
-  <si>
-    <t>THOMPSON</t>
-  </si>
-  <si>
-    <t>Yosef Hill</t>
-  </si>
-  <si>
-    <t>HILL</t>
-  </si>
-  <si>
-    <t>Mary Shelley</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>SHELLEY</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Albus Dumbledore</t>
-  </si>
-  <si>
-    <t>DUMBLEDORE</t>
-  </si>
-  <si>
-    <t>Jackson Harris</t>
-  </si>
-  <si>
-    <t>Team Kappa</t>
-  </si>
-  <si>
-    <t>HARRIS</t>
-  </si>
-  <si>
-    <t>Oscar Wilde</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>WILDE</t>
-  </si>
-  <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Uriel Wright</t>
-  </si>
-  <si>
-    <t>WRIGHT</t>
-  </si>
-  <si>
-    <t>Emily Bronte</t>
-  </si>
-  <si>
-    <t>BRONTE</t>
-  </si>
-  <si>
-    <t>Philip K Dick</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Pool F</t>
-  </si>
-  <si>
-    <t>Ygritte</t>
-  </si>
-  <si>
-    <t>YGRITTE</t>
-  </si>
-  <si>
-    <t>George Orwell</t>
-  </si>
-  <si>
-    <t>ORWELL</t>
-  </si>
-  <si>
-    <t>Quentin Blake</t>
-  </si>
-  <si>
-    <t>Team Rho</t>
-  </si>
-  <si>
-    <t>BLAKE</t>
-  </si>
-  <si>
-    <t>Pool G</t>
+    <t>Ray Bradbury</t>
+  </si>
+  <si>
+    <t>BRADBURY</t>
+  </si>
+  <si>
+    <t>Bilbo Baggins</t>
+  </si>
+  <si>
+    <t>Pool DD</t>
+  </si>
+  <si>
+    <t>Nathan Lee</t>
+  </si>
+  <si>
+    <t>LEE</t>
   </si>
   <si>
     <t>Kaden Martin</t>
@@ -260,490 +743,7 @@
     <t>MARTIN</t>
   </si>
   <si>
-    <t>William Wright</t>
-  </si>
-  <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
-    <t>Sylvia Plath</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>PLATH</t>
-  </si>
-  <si>
-    <t>Pool H</t>
-  </si>
-  <si>
-    <t>Xavier Lopez</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>Herman Melville</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>MELVILLE</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>Pool I</t>
-  </si>
-  <si>
-    <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>HALL</t>
-  </si>
-  <si>
-    <t>Caleb Wilson</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>Katniss Everdeen</t>
-  </si>
-  <si>
-    <t>EVERDEEN</t>
-  </si>
-  <si>
-    <t>Pool J</t>
-  </si>
-  <si>
-    <t>Dylan Moore</t>
-  </si>
-  <si>
-    <t>MOORE</t>
-  </si>
-  <si>
-    <t>Sebastian Allen</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>ALLEN</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Pool K</t>
-  </si>
-  <si>
-    <t>Ulysses Hernandez</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>Charles Dickens</t>
-  </si>
-  <si>
-    <t>DICKENS</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>Pool L</t>
-  </si>
-  <si>
-    <t>Daniel Defoe</t>
-  </si>
-  <si>
-    <t>DEFOE</t>
-  </si>
-  <si>
-    <t>Parker Lewis</t>
-  </si>
-  <si>
-    <t>LEWIS</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>Pool M</t>
-  </si>
-  <si>
-    <t>Zachary Adams</t>
-  </si>
-  <si>
-    <t>ADAMS</t>
-  </si>
-  <si>
     <t>Cersei Lannister</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>Pool N</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>Quirinus Quirrell</t>
-  </si>
-  <si>
-    <t>QUIRRELL</t>
-  </si>
-  <si>
-    <t>Pool O</t>
-  </si>
-  <si>
-    <t>Michael Lewis</t>
-  </si>
-  <si>
-    <t>Arthur Conan</t>
-  </si>
-  <si>
-    <t>CONAN</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Pool P</t>
-  </si>
-  <si>
-    <t>Luke Rodriguez</t>
-  </si>
-  <si>
-    <t>Team Beta</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>Robert Young</t>
-  </si>
-  <si>
-    <t>YOUNG</t>
-  </si>
-  <si>
-    <t>Nathaniel Hawthorne</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>HAWTHORNE</t>
-  </si>
-  <si>
-    <t>Pool Q</t>
-  </si>
-  <si>
-    <t>Steven Hernandez</t>
-  </si>
-  <si>
-    <t>Isaac White</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>Lewis Carroll</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>CARROLL</t>
-  </si>
-  <si>
-    <t>Pool R</t>
-  </si>
-  <si>
-    <t>Liam Thompson</t>
-  </si>
-  <si>
-    <t>Mason Martinez</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>Xavier Herbert</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>HERBERT</t>
-  </si>
-  <si>
-    <t>Pool S</t>
-  </si>
-  <si>
-    <t>Nolan Clark</t>
-  </si>
-  <si>
-    <t>Hudson Jackson</t>
-  </si>
-  <si>
-    <t>JACKSON</t>
-  </si>
-  <si>
-    <t>Ursula K Le Guin</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>LE GUIN</t>
-  </si>
-  <si>
-    <t>Pool T</t>
-  </si>
-  <si>
-    <t>Victor Lopez</t>
-  </si>
-  <si>
-    <t>William Hill</t>
-  </si>
-  <si>
-    <t>William Shakespeare</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>SHAKESPEARE</t>
-  </si>
-  <si>
-    <t>Pool U</t>
-  </si>
-  <si>
-    <t>Xavier Scott</t>
-  </si>
-  <si>
-    <t>SCOTT</t>
-  </si>
-  <si>
-    <t>Isaac Asimov</t>
-  </si>
-  <si>
-    <t>ASIMOV</t>
-  </si>
-  <si>
-    <t>Ray Bradbury</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>BRADBURY</t>
-  </si>
-  <si>
-    <t>Pool V</t>
-  </si>
-  <si>
-    <t>Vincent King</t>
-  </si>
-  <si>
-    <t>KING</t>
-  </si>
-  <si>
-    <t>Jane Austen</t>
-  </si>
-  <si>
-    <t>AUSTEN</t>
-  </si>
-  <si>
-    <t>Thomas Hardy</t>
-  </si>
-  <si>
-    <t>HARDY</t>
-  </si>
-  <si>
-    <t>Pool W</t>
-  </si>
-  <si>
-    <t>Oliver Walker</t>
-  </si>
-  <si>
-    <t>WALKER</t>
-  </si>
-  <si>
-    <t>Finn Anderson</t>
-  </si>
-  <si>
-    <t>ANDERSON</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
-  </si>
-  <si>
-    <t>Pool X</t>
-  </si>
-  <si>
-    <t>Quentin Allen</t>
-  </si>
-  <si>
-    <t>Quinn Walker</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Pool Y</t>
-  </si>
-  <si>
-    <t>Thomas King</t>
-  </si>
-  <si>
-    <t>Tristan Young</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>Pool Z</t>
-  </si>
-  <si>
-    <t>Bram Stoker</t>
-  </si>
-  <si>
-    <t>STOKER</t>
-  </si>
-  <si>
-    <t>Ryan Hall</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Pool AA</t>
-  </si>
-  <si>
-    <t>Owen Rodriguez</t>
-  </si>
-  <si>
-    <t>Virginia Woolf</t>
-  </si>
-  <si>
-    <t>WOOLF</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>Pool BB</t>
-  </si>
-  <si>
-    <t>Benjamin Evans</t>
-  </si>
-  <si>
-    <t>EVANS</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>Frodo Baggins</t>
-  </si>
-  <si>
-    <t>BAGGINS</t>
-  </si>
-  <si>
-    <t>Pool CC</t>
-  </si>
-  <si>
-    <t>Yosef Green</t>
-  </si>
-  <si>
-    <t>GREEN</t>
-  </si>
-  <si>
-    <t>Jon Snow</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>Pool DD</t>
-  </si>
-  <si>
-    <t>Nathan Lee</t>
-  </si>
-  <si>
-    <t>LEE</t>
-  </si>
-  <si>
-    <t>Bilbo Baggins</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -1959,10 +1959,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -1970,13 +1970,13 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -1984,808 +1984,808 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="D38" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="D39" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C41" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C43" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B44" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="D44" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B45" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="D45" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B46" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="D46" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B47" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="D47" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B48" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B49" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="D51" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C52" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D52" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="D53" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B54" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C54" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B55" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C55" t="s">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="D55" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B56" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C56" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="D56" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C57" t="s">
-        <v>157</v>
+        <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B58" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C58" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>19</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B59" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C59" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D59" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B60" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C60" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D60" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B61" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B62" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C62" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D62" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B63" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C63" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="D63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C64" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="D64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B65" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C65" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D65" t="s">
-        <v>176</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B66" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C66" t="s">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="D66" t="s">
         <v>179</v>
@@ -2799,7 +2799,7 @@
         <v>181</v>
       </c>
       <c r="C67" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="D67" t="s">
         <v>182</v>
@@ -2813,10 +2813,10 @@
         <v>183</v>
       </c>
       <c r="C68" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D68" t="s">
-        <v>184</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69">
@@ -2824,136 +2824,136 @@
         <v>180</v>
       </c>
       <c r="B69" t="s">
+        <v>184</v>
+      </c>
+      <c r="C69" t="s">
+        <v>104</v>
+      </c>
+      <c r="D69" t="s">
         <v>185</v>
-      </c>
-      <c r="C69" t="s">
-        <v>27</v>
-      </c>
-      <c r="D69" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>186</v>
+      </c>
+      <c r="B70" t="s">
         <v>187</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" t="s">
         <v>188</v>
-      </c>
-      <c r="C70" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D71" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B72" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C72" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="D72" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B73" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C73" t="s">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="D73" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>192</v>
+      </c>
+      <c r="B74" t="s">
         <v>194</v>
       </c>
-      <c r="B74" t="s">
-        <v>196</v>
-      </c>
       <c r="C74" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D74" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B75" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C75" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="D75" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>197</v>
+      </c>
+      <c r="B76" t="s">
+        <v>198</v>
+      </c>
+      <c r="C76" t="s">
+        <v>31</v>
+      </c>
+      <c r="D76" t="s">
         <v>199</v>
-      </c>
-      <c r="B76" t="s">
-        <v>200</v>
-      </c>
-      <c r="C76" t="s">
-        <v>21</v>
-      </c>
-      <c r="D76" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B77" t="s">
+        <v>200</v>
+      </c>
+      <c r="C77" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77" t="s">
         <v>201</v>
-      </c>
-      <c r="C77" t="s">
-        <v>50</v>
-      </c>
-      <c r="D77" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B78" t="s">
         <v>202</v>
       </c>
       <c r="C78" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="D78" t="s">
         <v>203</v>
@@ -2967,7 +2967,7 @@
         <v>205</v>
       </c>
       <c r="C79" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="D79" t="s">
         <v>206</v>
@@ -2981,10 +2981,10 @@
         <v>207</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="D80" t="s">
-        <v>91</v>
+        <v>208</v>
       </c>
     </row>
     <row r="81">
@@ -2992,139 +2992,139 @@
         <v>204</v>
       </c>
       <c r="B81" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C81" t="s">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="D81" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="D82" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B83" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C83" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="D83" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B84" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C84" t="s">
-        <v>170</v>
+        <v>37</v>
       </c>
       <c r="D84" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B85" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C85" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>218</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B86" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C86" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="D86" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B87" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D87" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B88" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="D88" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B89" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C89" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D89" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C90" t="s">
-        <v>178</v>
+        <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
     </row>
     <row r="91">
@@ -3135,7 +3135,7 @@
         <v>231</v>
       </c>
       <c r="C91" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="D91" t="s">
         <v>232</v>
@@ -3149,10 +3149,10 @@
         <v>233</v>
       </c>
       <c r="C92" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="D92" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
     </row>
     <row r="93">
@@ -3160,13 +3160,13 @@
         <v>230</v>
       </c>
       <c r="B93" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C93" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="D93" t="s">
-        <v>235</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -29,6 +29,7 @@
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Tree 4'!$A$1:$K$38</definedName>
     <definedName localSheetId="9" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$46</definedName>
     <definedName localSheetId="10" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$45</definedName>
+    <definedName localSheetId="11" name="_xlnm.Print_Area">'Tags'!$A$1:$A$182</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$271</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -1578,13 +1579,13 @@
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -4999,7 +5000,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="110"/>
+    <col customWidth="true" max="1" min="1" width="88"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -146,6 +146,300 @@
     <t>YOUNG</t>
   </si>
   <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>LANNISTER</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Steven Hernandez</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>Ryan Hall</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>HALL</t>
+  </si>
+  <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Gabriel Thomas</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>THOMAS</t>
+  </si>
+  <si>
+    <t>Lewis Carroll</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>CARROLL</t>
+  </si>
+  <si>
+    <t>Ygritte</t>
+  </si>
+  <si>
+    <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
+    <t>Quentin Allen</t>
+  </si>
+  <si>
+    <t>ALLEN</t>
+  </si>
+  <si>
+    <t>Parker Lewis</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>LEWIS</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Pool F</t>
+  </si>
+  <si>
+    <t>Caleb Wilson</t>
+  </si>
+  <si>
+    <t>WILSON</t>
+  </si>
+  <si>
+    <t>Yosef Hill</t>
+  </si>
+  <si>
+    <t>HILL</t>
+  </si>
+  <si>
+    <t>Yann Martel</t>
+  </si>
+  <si>
+    <t>MARTEL</t>
+  </si>
+  <si>
+    <t>Pool G</t>
+  </si>
+  <si>
+    <t>Aaron Thompson</t>
+  </si>
+  <si>
+    <t>Nolan Clark</t>
+  </si>
+  <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>Pool H</t>
+  </si>
+  <si>
+    <t>Isaac White</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>WHITE</t>
+  </si>
+  <si>
+    <t>Nathaniel Hawthorne</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>HAWTHORNE</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Pool I</t>
+  </si>
+  <si>
+    <t>Uriel Wright</t>
+  </si>
+  <si>
+    <t>WRIGHT</t>
+  </si>
+  <si>
+    <t>Quentin Blake</t>
+  </si>
+  <si>
+    <t>Team Rho</t>
+  </si>
+  <si>
+    <t>BLAKE</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>Pool J</t>
+  </si>
+  <si>
+    <t>Xavier Scott</t>
+  </si>
+  <si>
+    <t>SCOTT</t>
+  </si>
+  <si>
+    <t>Isaac Asimov</t>
+  </si>
+  <si>
+    <t>ASIMOV</t>
+  </si>
+  <si>
+    <t>Xavier Herbert</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>HERBERT</t>
+  </si>
+  <si>
+    <t>Pool K</t>
+  </si>
+  <si>
+    <t>Victor Lopez</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>Charles Dickens</t>
+  </si>
+  <si>
+    <t>DICKENS</t>
+  </si>
+  <si>
+    <t>Frodo Baggins</t>
+  </si>
+  <si>
+    <t>BAGGINS</t>
+  </si>
+  <si>
+    <t>Pool L</t>
+  </si>
+  <si>
+    <t>Elijah Taylor</t>
+  </si>
+  <si>
+    <t>TAYLOR</t>
+  </si>
+  <si>
+    <t>Oscar Wilde</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>WILDE</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>Pool M</t>
+  </si>
+  <si>
+    <t>Bram Stoker</t>
+  </si>
+  <si>
+    <t>STOKER</t>
+  </si>
+  <si>
+    <t>Emily Bronte</t>
+  </si>
+  <si>
+    <t>BRONTE</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>Pool N</t>
+  </si>
+  <si>
+    <t>Arthur Conan</t>
+  </si>
+  <si>
+    <t>CONAN</t>
+  </si>
+  <si>
+    <t>George Orwell</t>
+  </si>
+  <si>
+    <t>ORWELL</t>
+  </si>
+  <si>
     <t>Virginia Woolf</t>
   </si>
   <si>
@@ -155,300 +449,6 @@
     <t>WOOLF</t>
   </si>
   <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Steven Hernandez</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>Ryan Hall</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>HALL</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Gabriel Thomas</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>THOMAS</t>
-  </si>
-  <si>
-    <t>Lewis Carroll</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>CARROLL</t>
-  </si>
-  <si>
-    <t>Ygritte</t>
-  </si>
-  <si>
-    <t>YGRITTE</t>
-  </si>
-  <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Quentin Allen</t>
-  </si>
-  <si>
-    <t>ALLEN</t>
-  </si>
-  <si>
-    <t>Parker Lewis</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
-    <t>LEWIS</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Pool F</t>
-  </si>
-  <si>
-    <t>Caleb Wilson</t>
-  </si>
-  <si>
-    <t>WILSON</t>
-  </si>
-  <si>
-    <t>Yosef Hill</t>
-  </si>
-  <si>
-    <t>HILL</t>
-  </si>
-  <si>
-    <t>Yann Martel</t>
-  </si>
-  <si>
-    <t>MARTEL</t>
-  </si>
-  <si>
-    <t>Pool G</t>
-  </si>
-  <si>
-    <t>Aaron Thompson</t>
-  </si>
-  <si>
-    <t>Nolan Clark</t>
-  </si>
-  <si>
-    <t>Katniss Everdeen</t>
-  </si>
-  <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
-    <t>EVERDEEN</t>
-  </si>
-  <si>
-    <t>Pool H</t>
-  </si>
-  <si>
-    <t>Isaac White</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>Nathaniel Hawthorne</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>HAWTHORNE</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Pool I</t>
-  </si>
-  <si>
-    <t>Uriel Wright</t>
-  </si>
-  <si>
-    <t>WRIGHT</t>
-  </si>
-  <si>
-    <t>Quentin Blake</t>
-  </si>
-  <si>
-    <t>Team Rho</t>
-  </si>
-  <si>
-    <t>BLAKE</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>Pool J</t>
-  </si>
-  <si>
-    <t>Xavier Scott</t>
-  </si>
-  <si>
-    <t>SCOTT</t>
-  </si>
-  <si>
-    <t>Isaac Asimov</t>
-  </si>
-  <si>
-    <t>ASIMOV</t>
-  </si>
-  <si>
-    <t>Xavier Herbert</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>HERBERT</t>
-  </si>
-  <si>
-    <t>Pool K</t>
-  </si>
-  <si>
-    <t>Victor Lopez</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>Charles Dickens</t>
-  </si>
-  <si>
-    <t>DICKENS</t>
-  </si>
-  <si>
-    <t>Frodo Baggins</t>
-  </si>
-  <si>
-    <t>BAGGINS</t>
-  </si>
-  <si>
-    <t>Pool L</t>
-  </si>
-  <si>
-    <t>Elijah Taylor</t>
-  </si>
-  <si>
-    <t>TAYLOR</t>
-  </si>
-  <si>
-    <t>Oscar Wilde</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>WILDE</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>Pool M</t>
-  </si>
-  <si>
-    <t>Bram Stoker</t>
-  </si>
-  <si>
-    <t>STOKER</t>
-  </si>
-  <si>
-    <t>Emily Bronte</t>
-  </si>
-  <si>
-    <t>BRONTE</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Pool N</t>
-  </si>
-  <si>
-    <t>Arthur Conan</t>
-  </si>
-  <si>
-    <t>CONAN</t>
-  </si>
-  <si>
-    <t>George Orwell</t>
-  </si>
-  <si>
-    <t>ORWELL</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>LANNISTER</t>
-  </si>
-  <si>
     <t>Pool O</t>
   </si>
   <si>
@@ -512,237 +512,237 @@
     <t>Robert Young</t>
   </si>
   <si>
+    <t>Kaden Martin</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Pool S</t>
+  </si>
+  <si>
+    <t>Hudson Jackson</t>
+  </si>
+  <si>
+    <t>JACKSON</t>
+  </si>
+  <si>
+    <t>Mary Shelley</t>
+  </si>
+  <si>
+    <t>SHELLEY</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>Pool T</t>
+  </si>
+  <si>
+    <t>Paul Hall</t>
+  </si>
+  <si>
+    <t>Quinn Walker</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Pool U</t>
+  </si>
+  <si>
+    <t>Dylan Moore</t>
+  </si>
+  <si>
+    <t>MOORE</t>
+  </si>
+  <si>
+    <t>William Wright</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>Pool V</t>
+  </si>
+  <si>
+    <t>Thomas King</t>
+  </si>
+  <si>
+    <t>KING</t>
+  </si>
+  <si>
+    <t>Sebastian Allen</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Pool W</t>
+  </si>
+  <si>
+    <t>Jackson Harris</t>
+  </si>
+  <si>
+    <t>HARRIS</t>
+  </si>
+  <si>
+    <t>Vincent King</t>
+  </si>
+  <si>
+    <t>Albus Dumbledore</t>
+  </si>
+  <si>
+    <t>DUMBLEDORE</t>
+  </si>
+  <si>
+    <t>Pool X</t>
+  </si>
+  <si>
+    <t>William Hill</t>
+  </si>
+  <si>
+    <t>Philip K Dick</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>Pool Y</t>
+  </si>
+  <si>
+    <t>Benjamin Evans</t>
+  </si>
+  <si>
+    <t>EVANS</t>
+  </si>
+  <si>
+    <t>Herman Melville</t>
+  </si>
+  <si>
+    <t>MELVILLE</t>
+  </si>
+  <si>
+    <t>Ursula K Le Guin</t>
+  </si>
+  <si>
+    <t>LE GUIN</t>
+  </si>
+  <si>
+    <t>Pool Z</t>
+  </si>
+  <si>
+    <t>Yosef Green</t>
+  </si>
+  <si>
+    <t>GREEN</t>
+  </si>
+  <si>
+    <t>Daniel Defoe</t>
+  </si>
+  <si>
+    <t>DEFOE</t>
+  </si>
+  <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>Pool AA</t>
+  </si>
+  <si>
+    <t>Zachary Adams</t>
+  </si>
+  <si>
+    <t>ADAMS</t>
+  </si>
+  <si>
+    <t>Jane Austen</t>
+  </si>
+  <si>
+    <t>AUSTEN</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>Pool AB</t>
+  </si>
+  <si>
+    <t>Ulysses Hernandez</t>
+  </si>
+  <si>
+    <t>Fyodor Dostoevsky</t>
+  </si>
+  <si>
+    <t>DOSTOEVSKY</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>Pool AC</t>
+  </si>
+  <si>
+    <t>Kurt Vonnegut</t>
+  </si>
+  <si>
+    <t>VONNEGUT</t>
+  </si>
+  <si>
+    <t>Ray Bradbury</t>
+  </si>
+  <si>
+    <t>BRADBURY</t>
+  </si>
+  <si>
+    <t>Bilbo Baggins</t>
+  </si>
+  <si>
+    <t>Pool AD</t>
+  </si>
+  <si>
+    <t>Nathan Lee</t>
+  </si>
+  <si>
+    <t>LEE</t>
+  </si>
+  <si>
     <t>Thomas Hardy</t>
   </si>
   <si>
     <t>HARDY</t>
   </si>
   <si>
-    <t>Zachary Adams</t>
-  </si>
-  <si>
-    <t>ADAMS</t>
-  </si>
-  <si>
-    <t>Pool S</t>
-  </si>
-  <si>
-    <t>Hudson Jackson</t>
-  </si>
-  <si>
-    <t>JACKSON</t>
-  </si>
-  <si>
-    <t>Mary Shelley</t>
-  </si>
-  <si>
-    <t>SHELLEY</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>Pool T</t>
-  </si>
-  <si>
-    <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>Quinn Walker</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Pool U</t>
-  </si>
-  <si>
-    <t>Dylan Moore</t>
-  </si>
-  <si>
-    <t>MOORE</t>
-  </si>
-  <si>
-    <t>William Wright</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>Pool V</t>
-  </si>
-  <si>
-    <t>Thomas King</t>
-  </si>
-  <si>
-    <t>KING</t>
-  </si>
-  <si>
-    <t>Sebastian Allen</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>Pool W</t>
-  </si>
-  <si>
-    <t>Jackson Harris</t>
-  </si>
-  <si>
-    <t>HARRIS</t>
-  </si>
-  <si>
-    <t>Vincent King</t>
-  </si>
-  <si>
-    <t>Albus Dumbledore</t>
-  </si>
-  <si>
-    <t>DUMBLEDORE</t>
-  </si>
-  <si>
-    <t>Pool X</t>
-  </si>
-  <si>
-    <t>William Hill</t>
-  </si>
-  <si>
-    <t>Philip K Dick</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>Pool Y</t>
-  </si>
-  <si>
-    <t>Benjamin Evans</t>
-  </si>
-  <si>
-    <t>EVANS</t>
-  </si>
-  <si>
-    <t>Herman Melville</t>
-  </si>
-  <si>
-    <t>MELVILLE</t>
-  </si>
-  <si>
-    <t>Ursula K Le Guin</t>
-  </si>
-  <si>
-    <t>LE GUIN</t>
-  </si>
-  <si>
-    <t>Pool Z</t>
-  </si>
-  <si>
-    <t>Yosef Green</t>
-  </si>
-  <si>
-    <t>GREEN</t>
-  </si>
-  <si>
-    <t>Daniel Defoe</t>
-  </si>
-  <si>
-    <t>DEFOE</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>Pool AA</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
-  </si>
-  <si>
-    <t>Jane Austen</t>
-  </si>
-  <si>
-    <t>AUSTEN</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>Pool BB</t>
-  </si>
-  <si>
-    <t>Ulysses Hernandez</t>
-  </si>
-  <si>
-    <t>Fyodor Dostoevsky</t>
-  </si>
-  <si>
-    <t>DOSTOEVSKY</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Pool CC</t>
-  </si>
-  <si>
-    <t>Kurt Vonnegut</t>
-  </si>
-  <si>
-    <t>VONNEGUT</t>
-  </si>
-  <si>
-    <t>Ray Bradbury</t>
-  </si>
-  <si>
-    <t>BRADBURY</t>
-  </si>
-  <si>
-    <t>Bilbo Baggins</t>
-  </si>
-  <si>
-    <t>Pool DD</t>
-  </si>
-  <si>
-    <t>Nathan Lee</t>
-  </si>
-  <si>
-    <t>LEE</t>
-  </si>
-  <si>
-    <t>Kaden Martin</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
     <t>Cersei Lannister</t>
   </si>
   <si>
@@ -1043,31 +1043,31 @@
     <t>AA3</t>
   </si>
   <si>
-    <t>BB1</t>
-  </si>
-  <si>
-    <t>BB2</t>
-  </si>
-  <si>
-    <t>BB3</t>
-  </si>
-  <si>
-    <t>CC1</t>
-  </si>
-  <si>
-    <t>CC2</t>
-  </si>
-  <si>
-    <t>CC3</t>
-  </si>
-  <si>
-    <t>DD1</t>
-  </si>
-  <si>
-    <t>DD2</t>
-  </si>
-  <si>
-    <t>DD3</t>
+    <t>AB1</t>
+  </si>
+  <si>
+    <t>AB2</t>
+  </si>
+  <si>
+    <t>AB3</t>
+  </si>
+  <si>
+    <t>AC1</t>
+  </si>
+  <si>
+    <t>AC2</t>
+  </si>
+  <si>
+    <t>AC3</t>
+  </si>
+  <si>
+    <t>AD1</t>
+  </si>
+  <si>
+    <t>AD2</t>
+  </si>
+  <si>
+    <t>AD3</t>
   </si>
   <si>
     <t>Round 1 - Match 1</t>
@@ -2645,7 +2645,7 @@
         <v>158</v>
       </c>
       <c r="C56" t="s">
-        <v>135</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
         <v>159</v>
@@ -2659,7 +2659,7 @@
         <v>160</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="D57" t="s">
         <v>161</v>
@@ -3009,7 +3009,7 @@
         <v>212</v>
       </c>
       <c r="C82" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="D82" t="s">
         <v>213</v>
@@ -3037,7 +3037,7 @@
         <v>216</v>
       </c>
       <c r="C84" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="D84" t="s">
         <v>217</v>
@@ -3149,7 +3149,7 @@
         <v>233</v>
       </c>
       <c r="C92" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D92" t="s">
         <v>234</v>
@@ -3166,7 +3166,7 @@
         <v>24</v>
       </c>
       <c r="D93" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -3770,7 +3770,7 @@
         <f>"2. " &amp; data!$B$83</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O222)</f>
+        <f>CONCATENATE("Pool AB-1st ",'Pool Matches'!O222)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3809,7 +3809,7 @@
         <f>"1. " &amp; data!$B$85</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O239)</f>
+        <f>CONCATENATE("Pool AC-1st ",'Pool Matches'!O239)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3854,7 +3854,7 @@
         <f>'data'!$A$90</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
+        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O256)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -13129,7 +13129,7 @@
     </row>
     <row r="100">
       <c r="A100" s="14" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O223)</f>
+        <f>CONCATENATE("Pool AB-2nd ",'Pool Matches'!O223)</f>
       </c>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
@@ -13148,7 +13148,7 @@
       <c r="M100" s="18"/>
       <c r="N100" s="18"/>
       <c r="O100" s="14" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O222)</f>
+        <f>CONCATENATE("Pool AB-1st ",'Pool Matches'!O222)</f>
       </c>
     </row>
     <row r="102">
@@ -13213,7 +13213,7 @@
     </row>
     <row r="108">
       <c r="A108" s="14" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O240)</f>
+        <f>CONCATENATE("Pool AC-2nd ",'Pool Matches'!O240)</f>
       </c>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -13232,7 +13232,7 @@
       <c r="M108" s="18"/>
       <c r="N108" s="18"/>
       <c r="O108" s="14" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O239)</f>
+        <f>CONCATENATE("Pool AC-1st ",'Pool Matches'!O239)</f>
       </c>
     </row>
     <row r="110">
@@ -13297,7 +13297,7 @@
     </row>
     <row r="116">
       <c r="A116" s="14" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
+        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O257)</f>
       </c>
       <c r="B116" s="18"/>
       <c r="C116" s="18"/>
@@ -13316,7 +13316,7 @@
       <c r="M116" s="18"/>
       <c r="N116" s="18"/>
       <c r="O116" s="14" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O256)</f>
+        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O256)</f>
       </c>
     </row>
     <row r="118">
@@ -15260,7 +15260,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O223)</f>
+        <f>CONCATENATE("Pool AB-2nd ",'Pool Matches'!O223)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -15307,7 +15307,7 @@
         <f>"3. " &amp; data!$B$42</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O240)</f>
+        <f>CONCATENATE("Pool AC-2nd ",'Pool Matches'!O240)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -15346,7 +15346,7 @@
         <f>"2. " &amp; data!$B$44</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O257)</f>
+        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O257)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -1582,7 +1582,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
@@ -4206,8 +4206,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
@@ -4607,8 +4607,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -1585,7 +1585,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
